--- a/research/traditional_assets/database/data/morocco/morocco_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_beverage_soft.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09615161952668347</v>
+        <v>0.09587453434419807</v>
       </c>
       <c r="C2">
-        <v>384.512017730847</v>
+        <v>382.3758423252565</v>
       </c>
       <c r="D2">
-        <v>367.912017730847</v>
+        <v>369.9478423252565</v>
       </c>
       <c r="E2">
-        <v>-174.4</v>
+        <v>-170.228</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.172000000000001</v>
       </c>
       <c r="G2">
         <v>16.6</v>
@@ -1451,28 +1451,28 @@
         <v>61.954</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2098516</v>
       </c>
       <c r="N2">
-        <v>61.954</v>
+        <v>61.7441484</v>
       </c>
       <c r="O2">
-        <v>19.82528</v>
+        <v>19.758127488</v>
       </c>
       <c r="P2">
-        <v>42.12872</v>
+        <v>41.986020912</v>
       </c>
       <c r="Q2">
-        <v>42.29972</v>
+        <v>42.157020912</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09615161952668347</v>
+        <v>0.09649746903454351</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6607579747196656</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>295.2276751761721</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09587453434419807</v>
+        <v>0.09559744916171269</v>
       </c>
       <c r="C3">
-        <v>382.3758423252565</v>
+        <v>380.2623225712605</v>
       </c>
       <c r="D3">
-        <v>369.9478423252565</v>
+        <v>372.0063225712605</v>
       </c>
       <c r="E3">
-        <v>-170.228</v>
+        <v>-166.056</v>
       </c>
       <c r="F3">
-        <v>4.172000000000001</v>
+        <v>8.344000000000001</v>
       </c>
       <c r="G3">
         <v>16.6</v>
@@ -1533,28 +1533,28 @@
         <v>61.954</v>
       </c>
       <c r="M3">
-        <v>0.2098516</v>
+        <v>0.4197032000000001</v>
       </c>
       <c r="N3">
-        <v>61.7441484</v>
+        <v>61.5342968</v>
       </c>
       <c r="O3">
-        <v>19.758127488</v>
+        <v>19.690974976</v>
       </c>
       <c r="P3">
-        <v>41.986020912</v>
+        <v>41.843321824</v>
       </c>
       <c r="Q3">
-        <v>42.157020912</v>
+        <v>42.014321824</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09649746903454351</v>
+        <v>0.09685037669562518</v>
       </c>
       <c r="T3">
-        <v>0.6607579747196656</v>
+        <v>0.6653575445964279</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>295.2276751761721</v>
+        <v>147.613837588086</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09559744916171269</v>
+        <v>0.09532036397922729</v>
       </c>
       <c r="C4">
-        <v>380.2623225712605</v>
+        <v>378.1718387696999</v>
       </c>
       <c r="D4">
-        <v>372.0063225712605</v>
+        <v>374.0878387696999</v>
       </c>
       <c r="E4">
-        <v>-166.056</v>
+        <v>-161.884</v>
       </c>
       <c r="F4">
-        <v>8.344000000000001</v>
+        <v>12.516</v>
       </c>
       <c r="G4">
         <v>16.6</v>
@@ -1615,28 +1615,28 @@
         <v>61.954</v>
       </c>
       <c r="M4">
-        <v>0.4197032000000001</v>
+        <v>0.6295548</v>
       </c>
       <c r="N4">
-        <v>61.5342968</v>
+        <v>61.3244452</v>
       </c>
       <c r="O4">
-        <v>19.690974976</v>
+        <v>19.623822464</v>
       </c>
       <c r="P4">
-        <v>41.843321824</v>
+        <v>41.700622736</v>
       </c>
       <c r="Q4">
-        <v>42.014321824</v>
+        <v>41.871622736</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09685037669562518</v>
+        <v>0.0972105608033271</v>
       </c>
       <c r="T4">
-        <v>0.6653575445964279</v>
+        <v>0.6700519509654949</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>147.613837588086</v>
+        <v>98.40922505872405</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09532036397922729</v>
+        <v>0.0950432787967419</v>
       </c>
       <c r="C5">
-        <v>378.1718387696999</v>
+        <v>376.1047797810187</v>
       </c>
       <c r="D5">
-        <v>374.0878387696999</v>
+        <v>376.1927797810187</v>
       </c>
       <c r="E5">
-        <v>-161.884</v>
+        <v>-157.712</v>
       </c>
       <c r="F5">
-        <v>12.516</v>
+        <v>16.688</v>
       </c>
       <c r="G5">
         <v>16.6</v>
@@ -1697,28 +1697,28 @@
         <v>61.954</v>
       </c>
       <c r="M5">
-        <v>0.6295548</v>
+        <v>0.8394064000000001</v>
       </c>
       <c r="N5">
-        <v>61.3244452</v>
+        <v>61.1145936</v>
       </c>
       <c r="O5">
-        <v>19.623822464</v>
+        <v>19.556669952</v>
       </c>
       <c r="P5">
-        <v>41.700622736</v>
+        <v>41.557923648</v>
       </c>
       <c r="Q5">
-        <v>41.871622736</v>
+        <v>41.728923648</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0972105608033271</v>
+        <v>0.09757824874660616</v>
       </c>
       <c r="T5">
-        <v>0.6700519509654949</v>
+        <v>0.6748441574672507</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>98.40922505872405</v>
+        <v>73.80691879404301</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0950432787967419</v>
+        <v>0.09476619361425652</v>
       </c>
       <c r="C6">
-        <v>376.1047797810187</v>
+        <v>374.0615432674449</v>
       </c>
       <c r="D6">
-        <v>376.1927797810187</v>
+        <v>378.3215432674449</v>
       </c>
       <c r="E6">
-        <v>-157.712</v>
+        <v>-153.54</v>
       </c>
       <c r="F6">
-        <v>16.688</v>
+        <v>20.86</v>
       </c>
       <c r="G6">
         <v>16.6</v>
@@ -1779,28 +1779,28 @@
         <v>61.954</v>
       </c>
       <c r="M6">
-        <v>0.8394064000000001</v>
+        <v>1.049258</v>
       </c>
       <c r="N6">
-        <v>61.1145936</v>
+        <v>60.904742</v>
       </c>
       <c r="O6">
-        <v>19.556669952</v>
+        <v>19.48951744</v>
       </c>
       <c r="P6">
-        <v>41.557923648</v>
+        <v>41.41522456</v>
       </c>
       <c r="Q6">
-        <v>41.728923648</v>
+        <v>41.58622456</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09757824874660616</v>
+        <v>0.09795367748869108</v>
       </c>
       <c r="T6">
-        <v>0.6748441574672507</v>
+        <v>0.6797372525269382</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>73.80691879404301</v>
+        <v>59.04553503523442</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09476619361425652</v>
+        <v>0.09448910843177112</v>
       </c>
       <c r="C7">
-        <v>374.0615432674449</v>
+        <v>372.0425359434417</v>
       </c>
       <c r="D7">
-        <v>378.3215432674449</v>
+        <v>380.4745359434417</v>
       </c>
       <c r="E7">
-        <v>-153.54</v>
+        <v>-149.368</v>
       </c>
       <c r="F7">
-        <v>20.86</v>
+        <v>25.032</v>
       </c>
       <c r="G7">
         <v>16.6</v>
@@ -1861,28 +1861,28 @@
         <v>61.954</v>
       </c>
       <c r="M7">
-        <v>1.049258</v>
+        <v>1.2591096</v>
       </c>
       <c r="N7">
-        <v>60.904742</v>
+        <v>60.6948904</v>
       </c>
       <c r="O7">
-        <v>19.48951744</v>
+        <v>19.422364928</v>
       </c>
       <c r="P7">
-        <v>41.41522456</v>
+        <v>41.272525472</v>
       </c>
       <c r="Q7">
-        <v>41.58622456</v>
+        <v>41.443525472</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09795367748869108</v>
+        <v>0.09833709407635227</v>
       </c>
       <c r="T7">
-        <v>0.6797372525269382</v>
+        <v>0.6847344559921509</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>59.04553503523442</v>
+        <v>49.20461252936201</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09448910843177112</v>
+        <v>0.09421202324928576</v>
       </c>
       <c r="C8">
-        <v>372.0425359434417</v>
+        <v>370.0481738347578</v>
       </c>
       <c r="D8">
-        <v>380.4745359434417</v>
+        <v>382.6521738347578</v>
       </c>
       <c r="E8">
-        <v>-149.368</v>
+        <v>-145.196</v>
       </c>
       <c r="F8">
-        <v>25.032</v>
+        <v>29.204</v>
       </c>
       <c r="G8">
         <v>16.6</v>
@@ -1943,28 +1943,28 @@
         <v>61.954</v>
       </c>
       <c r="M8">
-        <v>1.2591096</v>
+        <v>1.4689612</v>
       </c>
       <c r="N8">
-        <v>60.6948904</v>
+        <v>60.4850388</v>
       </c>
       <c r="O8">
-        <v>19.422364928</v>
+        <v>19.355212416</v>
       </c>
       <c r="P8">
-        <v>41.272525472</v>
+        <v>41.129826384</v>
       </c>
       <c r="Q8">
-        <v>41.443525472</v>
+        <v>41.300826384</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09833709407635227</v>
+        <v>0.0987287561820277</v>
       </c>
       <c r="T8">
-        <v>0.6847344559921509</v>
+        <v>0.689839126198551</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>49.20461252936202</v>
+        <v>42.17538216802459</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09421202324928575</v>
+        <v>0.09393493806680037</v>
       </c>
       <c r="C9">
-        <v>370.0481738347579</v>
+        <v>368.0788825464278</v>
       </c>
       <c r="D9">
-        <v>382.6521738347579</v>
+        <v>384.8548825464278</v>
       </c>
       <c r="E9">
-        <v>-145.196</v>
+        <v>-141.024</v>
       </c>
       <c r="F9">
-        <v>29.20400000000001</v>
+        <v>33.376</v>
       </c>
       <c r="G9">
         <v>16.6</v>
@@ -2025,28 +2025,28 @@
         <v>61.954</v>
       </c>
       <c r="M9">
-        <v>1.4689612</v>
+        <v>1.6788128</v>
       </c>
       <c r="N9">
-        <v>60.4850388</v>
+        <v>60.2751872</v>
       </c>
       <c r="O9">
-        <v>19.355212416</v>
+        <v>19.288059904</v>
       </c>
       <c r="P9">
-        <v>41.129826384</v>
+        <v>40.987127296</v>
       </c>
       <c r="Q9">
-        <v>41.300826384</v>
+        <v>41.158127296</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0987287561820277</v>
+        <v>0.09912893268130474</v>
       </c>
       <c r="T9">
-        <v>0.689839126198551</v>
+        <v>0.6950547674963946</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>42.17538216802458</v>
+        <v>36.90345939702151</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09393493806680037</v>
+        <v>0.09365785288431498</v>
       </c>
       <c r="C10">
-        <v>368.0788825464278</v>
+        <v>366.1350975400787</v>
       </c>
       <c r="D10">
-        <v>384.8548825464278</v>
+        <v>387.0830975400787</v>
       </c>
       <c r="E10">
-        <v>-141.024</v>
+        <v>-136.852</v>
       </c>
       <c r="F10">
-        <v>33.376</v>
+        <v>37.548</v>
       </c>
       <c r="G10">
         <v>16.6</v>
@@ -2107,28 +2107,28 @@
         <v>61.954</v>
       </c>
       <c r="M10">
-        <v>1.6788128</v>
+        <v>1.8886644</v>
       </c>
       <c r="N10">
-        <v>60.2751872</v>
+        <v>60.0653356</v>
       </c>
       <c r="O10">
-        <v>19.288059904</v>
+        <v>19.220907392</v>
       </c>
       <c r="P10">
-        <v>40.987127296</v>
+        <v>40.844428208</v>
       </c>
       <c r="Q10">
-        <v>41.158127296</v>
+        <v>41.015428208</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09912893268130474</v>
+        <v>0.099537904268478</v>
       </c>
       <c r="T10">
-        <v>0.6950547674963946</v>
+        <v>0.7003850382733117</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.90345939702151</v>
+        <v>32.80307501957468</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09365785288431498</v>
+        <v>0.0933807677018296</v>
       </c>
       <c r="C11">
-        <v>366.1350975400787</v>
+        <v>364.217264420929</v>
       </c>
       <c r="D11">
-        <v>387.0830975400787</v>
+        <v>389.337264420929</v>
       </c>
       <c r="E11">
-        <v>-136.852</v>
+        <v>-132.68</v>
       </c>
       <c r="F11">
-        <v>37.548</v>
+        <v>41.72</v>
       </c>
       <c r="G11">
         <v>16.6</v>
@@ -2189,28 +2189,28 @@
         <v>61.954</v>
       </c>
       <c r="M11">
-        <v>1.8886644</v>
+        <v>2.098516</v>
       </c>
       <c r="N11">
-        <v>60.0653356</v>
+        <v>59.855484</v>
       </c>
       <c r="O11">
-        <v>19.220907392</v>
+        <v>19.15375488</v>
       </c>
       <c r="P11">
-        <v>40.844428208</v>
+        <v>40.70172912</v>
       </c>
       <c r="Q11">
-        <v>41.015428208</v>
+        <v>40.87272912</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.099537904268478</v>
+        <v>0.09995596411314399</v>
       </c>
       <c r="T11">
-        <v>0.7003850382733117</v>
+        <v>0.7058337595119381</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.80307501957468</v>
+        <v>29.52276751761721</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0933807677018296</v>
+        <v>0.0931036825193442</v>
       </c>
       <c r="C12">
-        <v>364.217264420929</v>
+        <v>362.3258392348735</v>
       </c>
       <c r="D12">
-        <v>389.337264420929</v>
+        <v>391.6178392348734</v>
       </c>
       <c r="E12">
-        <v>-132.68</v>
+        <v>-128.508</v>
       </c>
       <c r="F12">
-        <v>41.72000000000001</v>
+        <v>45.892</v>
       </c>
       <c r="G12">
         <v>16.6</v>
@@ -2271,28 +2271,28 @@
         <v>61.954</v>
       </c>
       <c r="M12">
-        <v>2.098516</v>
+        <v>2.3083676</v>
       </c>
       <c r="N12">
-        <v>59.855484</v>
+        <v>59.6456324</v>
       </c>
       <c r="O12">
-        <v>19.15375488</v>
+        <v>19.086602368</v>
       </c>
       <c r="P12">
-        <v>40.70172912</v>
+        <v>40.559030032</v>
       </c>
       <c r="Q12">
-        <v>40.87272912</v>
+        <v>40.730030032</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09995596411314399</v>
+        <v>0.1003834185610609</v>
       </c>
       <c r="T12">
-        <v>0.7058337595119381</v>
+        <v>0.7114049239244661</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.52276751761721</v>
+        <v>26.83887956147019</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0931036825193442</v>
+        <v>0.0928265973368588</v>
       </c>
       <c r="C13">
-        <v>362.3258392348735</v>
+        <v>360.4612887760692</v>
       </c>
       <c r="D13">
-        <v>391.6178392348734</v>
+        <v>393.9252887760692</v>
       </c>
       <c r="E13">
-        <v>-128.508</v>
+        <v>-124.336</v>
       </c>
       <c r="F13">
-        <v>45.892</v>
+        <v>50.064</v>
       </c>
       <c r="G13">
         <v>16.6</v>
@@ -2353,28 +2353,28 @@
         <v>61.954</v>
       </c>
       <c r="M13">
-        <v>2.3083676</v>
+        <v>2.5182192</v>
       </c>
       <c r="N13">
-        <v>59.6456324</v>
+        <v>59.4357808</v>
       </c>
       <c r="O13">
-        <v>19.086602368</v>
+        <v>19.019449856</v>
       </c>
       <c r="P13">
-        <v>40.559030032</v>
+        <v>40.416330944</v>
       </c>
       <c r="Q13">
-        <v>40.730030032</v>
+        <v>40.587330944</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1003834185610609</v>
+        <v>0.1008205878827941</v>
       </c>
       <c r="T13">
-        <v>0.7114049239244661</v>
+        <v>0.7171027057100062</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.83887956147019</v>
+        <v>24.60230626468101</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0928265973368588</v>
+        <v>0.09254951215437342</v>
       </c>
       <c r="C14">
-        <v>360.4612887760692</v>
+        <v>358.6240909054625</v>
       </c>
       <c r="D14">
-        <v>393.9252887760692</v>
+        <v>396.2600909054624</v>
       </c>
       <c r="E14">
-        <v>-124.336</v>
+        <v>-120.164</v>
       </c>
       <c r="F14">
-        <v>50.064</v>
+        <v>54.23600000000001</v>
       </c>
       <c r="G14">
         <v>16.6</v>
@@ -2435,28 +2435,28 @@
         <v>61.954</v>
       </c>
       <c r="M14">
-        <v>2.5182192</v>
+        <v>2.7280708</v>
       </c>
       <c r="N14">
-        <v>59.4357808</v>
+        <v>59.2259292</v>
       </c>
       <c r="O14">
-        <v>19.019449856</v>
+        <v>18.952297344</v>
       </c>
       <c r="P14">
-        <v>40.416330944</v>
+        <v>40.273631856</v>
       </c>
       <c r="Q14">
-        <v>40.587330944</v>
+        <v>40.444631856</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1008205878827941</v>
+        <v>0.1012678070739924</v>
       </c>
       <c r="T14">
-        <v>0.7171027057100062</v>
+        <v>0.722931470984869</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.60230626468101</v>
+        <v>22.70982116739786</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09254951215437342</v>
+        <v>0.09227242697188803</v>
       </c>
       <c r="C15">
-        <v>358.6240909054625</v>
+        <v>356.814734880709</v>
       </c>
       <c r="D15">
-        <v>396.2600909054624</v>
+        <v>398.6227348807089</v>
       </c>
       <c r="E15">
-        <v>-120.164</v>
+        <v>-115.992</v>
       </c>
       <c r="F15">
-        <v>54.23600000000001</v>
+        <v>58.40800000000002</v>
       </c>
       <c r="G15">
         <v>16.6</v>
@@ -2517,28 +2517,28 @@
         <v>61.954</v>
       </c>
       <c r="M15">
-        <v>2.7280708</v>
+        <v>2.937922400000001</v>
       </c>
       <c r="N15">
-        <v>59.2259292</v>
+        <v>59.0160776</v>
       </c>
       <c r="O15">
-        <v>18.952297344</v>
+        <v>18.885144832</v>
       </c>
       <c r="P15">
-        <v>40.273631856</v>
+        <v>40.130932768</v>
       </c>
       <c r="Q15">
-        <v>40.444631856</v>
+        <v>40.301932768</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1012678070739924</v>
+        <v>0.1017254267114977</v>
       </c>
       <c r="T15">
-        <v>0.722931470984869</v>
+        <v>0.7288957889405425</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.70982116739786</v>
+        <v>21.08769108401229</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09227242697188803</v>
+        <v>0.09199534178940265</v>
       </c>
       <c r="C16">
-        <v>356.814734880709</v>
+        <v>355.0337216979681</v>
       </c>
       <c r="D16">
-        <v>398.6227348807089</v>
+        <v>401.0137216979682</v>
       </c>
       <c r="E16">
-        <v>-115.992</v>
+        <v>-111.82</v>
       </c>
       <c r="F16">
-        <v>58.40800000000002</v>
+        <v>62.58000000000002</v>
       </c>
       <c r="G16">
         <v>16.6</v>
@@ -2599,28 +2599,28 @@
         <v>61.954</v>
       </c>
       <c r="M16">
-        <v>2.937922400000001</v>
+        <v>3.147774000000001</v>
       </c>
       <c r="N16">
-        <v>59.0160776</v>
+        <v>58.806226</v>
       </c>
       <c r="O16">
-        <v>18.885144832</v>
+        <v>18.81799232</v>
       </c>
       <c r="P16">
-        <v>40.130932768</v>
+        <v>39.98823368</v>
       </c>
       <c r="Q16">
-        <v>40.301932768</v>
+        <v>40.15923368</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1017254267114977</v>
+        <v>0.1021938138698855</v>
       </c>
       <c r="T16">
-        <v>0.7288957889405425</v>
+        <v>0.7350004437892909</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.08769108401229</v>
+        <v>19.6818450117448</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09199534178940265</v>
+        <v>0.09171825660691726</v>
       </c>
       <c r="C17">
-        <v>355.0337216979682</v>
+        <v>353.2815644460721</v>
       </c>
       <c r="D17">
-        <v>401.0137216979682</v>
+        <v>403.4335644460721</v>
       </c>
       <c r="E17">
-        <v>-111.82</v>
+        <v>-107.648</v>
       </c>
       <c r="F17">
-        <v>62.58000000000001</v>
+        <v>66.75200000000001</v>
       </c>
       <c r="G17">
         <v>16.6</v>
@@ -2681,28 +2681,28 @@
         <v>61.954</v>
       </c>
       <c r="M17">
-        <v>3.147774</v>
+        <v>3.3576256</v>
       </c>
       <c r="N17">
-        <v>58.806226</v>
+        <v>58.5963744</v>
       </c>
       <c r="O17">
-        <v>18.81799232</v>
+        <v>18.750839808</v>
       </c>
       <c r="P17">
-        <v>39.98823368</v>
+        <v>39.845534592</v>
       </c>
       <c r="Q17">
-        <v>40.15923368</v>
+        <v>40.016534592</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1021938138698855</v>
+        <v>0.1026733531034729</v>
       </c>
       <c r="T17">
-        <v>0.7350004437892909</v>
+        <v>0.7412504475630093</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.68184501174481</v>
+        <v>18.45172969851076</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09171825660691726</v>
+        <v>0.09144117142443188</v>
       </c>
       <c r="C18">
-        <v>353.2815644460721</v>
+        <v>351.5587886735955</v>
       </c>
       <c r="D18">
-        <v>403.4335644460721</v>
+        <v>405.8827886735955</v>
       </c>
       <c r="E18">
-        <v>-107.648</v>
+        <v>-103.476</v>
       </c>
       <c r="F18">
-        <v>66.75200000000001</v>
+        <v>70.92400000000001</v>
       </c>
       <c r="G18">
         <v>16.6</v>
@@ -2763,28 +2763,28 @@
         <v>61.954</v>
       </c>
       <c r="M18">
-        <v>3.3576256</v>
+        <v>3.5674772</v>
       </c>
       <c r="N18">
-        <v>58.5963744</v>
+        <v>58.3865228</v>
       </c>
       <c r="O18">
-        <v>18.750839808</v>
+        <v>18.683687296</v>
       </c>
       <c r="P18">
-        <v>39.845534592</v>
+        <v>39.702835504</v>
       </c>
       <c r="Q18">
-        <v>40.016534592</v>
+        <v>39.873835504</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1026733531034729</v>
+        <v>0.1031644474993155</v>
       </c>
       <c r="T18">
-        <v>0.7412504475630093</v>
+        <v>0.7476510538372994</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.45172969851076</v>
+        <v>17.36633383389248</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09144117142443188</v>
+        <v>0.09116408624194648</v>
       </c>
       <c r="C19">
-        <v>351.5587886735955</v>
+        <v>349.8659327693784</v>
       </c>
       <c r="D19">
-        <v>405.8827886735955</v>
+        <v>408.3619327693784</v>
       </c>
       <c r="E19">
-        <v>-103.476</v>
+        <v>-99.30399999999999</v>
       </c>
       <c r="F19">
-        <v>70.92400000000001</v>
+        <v>75.09600000000002</v>
       </c>
       <c r="G19">
         <v>16.6</v>
@@ -2845,28 +2845,28 @@
         <v>61.954</v>
       </c>
       <c r="M19">
-        <v>3.5674772</v>
+        <v>3.777328800000001</v>
       </c>
       <c r="N19">
-        <v>58.3865228</v>
+        <v>58.1766712</v>
       </c>
       <c r="O19">
-        <v>18.683687296</v>
+        <v>18.616534784</v>
       </c>
       <c r="P19">
-        <v>39.702835504</v>
+        <v>39.560136416</v>
       </c>
       <c r="Q19">
-        <v>39.873835504</v>
+        <v>39.731136416</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1031644474993155</v>
+        <v>0.1036675198072518</v>
       </c>
       <c r="T19">
-        <v>0.7476510538372994</v>
+        <v>0.7542077724597426</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.36633383389248</v>
+        <v>16.40153750978734</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0911640862419465</v>
+        <v>0.09088700105946111</v>
       </c>
       <c r="C20">
-        <v>349.8659327693782</v>
+        <v>348.2035483570787</v>
       </c>
       <c r="D20">
-        <v>408.3619327693782</v>
+        <v>410.8715483570787</v>
       </c>
       <c r="E20">
-        <v>-99.304</v>
+        <v>-95.13199999999999</v>
       </c>
       <c r="F20">
-        <v>75.096</v>
+        <v>79.26800000000001</v>
       </c>
       <c r="G20">
         <v>16.6</v>
@@ -2927,28 +2927,28 @@
         <v>61.954</v>
       </c>
       <c r="M20">
-        <v>3.7773288</v>
+        <v>3.987180400000001</v>
       </c>
       <c r="N20">
-        <v>58.1766712</v>
+        <v>57.9668196</v>
       </c>
       <c r="O20">
-        <v>18.616534784</v>
+        <v>18.549382272</v>
       </c>
       <c r="P20">
-        <v>39.560136416</v>
+        <v>39.41743732800001</v>
       </c>
       <c r="Q20">
-        <v>39.731136416</v>
+        <v>39.588437328</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1036675198072518</v>
+        <v>0.1041830136536557</v>
       </c>
       <c r="T20">
-        <v>0.7542077724597426</v>
+        <v>0.76092638536916</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.40153750978734</v>
+        <v>15.53829869348274</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09088700105946111</v>
+        <v>0.09060991587697571</v>
       </c>
       <c r="C21">
-        <v>348.2035483570787</v>
+        <v>346.5722007043658</v>
       </c>
       <c r="D21">
-        <v>410.8715483570787</v>
+        <v>413.4122007043658</v>
       </c>
       <c r="E21">
-        <v>-95.13199999999999</v>
+        <v>-90.95999999999999</v>
       </c>
       <c r="F21">
-        <v>79.26800000000001</v>
+        <v>83.44000000000001</v>
       </c>
       <c r="G21">
         <v>16.6</v>
@@ -3009,28 +3009,28 @@
         <v>61.954</v>
       </c>
       <c r="M21">
-        <v>3.987180400000001</v>
+        <v>4.197032</v>
       </c>
       <c r="N21">
-        <v>57.9668196</v>
+        <v>57.756968</v>
       </c>
       <c r="O21">
-        <v>18.549382272</v>
+        <v>18.48222976</v>
       </c>
       <c r="P21">
-        <v>39.41743732800001</v>
+        <v>39.27473824</v>
       </c>
       <c r="Q21">
-        <v>39.588437328</v>
+        <v>39.44573824</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1041830136536557</v>
+        <v>0.1047113948462196</v>
       </c>
       <c r="T21">
-        <v>0.76092638536916</v>
+        <v>0.7678129636013127</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.53829869348274</v>
+        <v>14.76138375880861</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09060991587697571</v>
+        <v>0.09033283069449033</v>
       </c>
       <c r="C22">
-        <v>346.5722007043658</v>
+        <v>344.9724691473872</v>
       </c>
       <c r="D22">
-        <v>413.4122007043658</v>
+        <v>415.9844691473872</v>
       </c>
       <c r="E22">
-        <v>-90.95999999999999</v>
+        <v>-86.78799999999998</v>
       </c>
       <c r="F22">
-        <v>83.44000000000001</v>
+        <v>87.61200000000002</v>
       </c>
       <c r="G22">
         <v>16.6</v>
@@ -3091,28 +3091,28 @@
         <v>61.954</v>
       </c>
       <c r="M22">
-        <v>4.197032</v>
+        <v>4.406883600000001</v>
       </c>
       <c r="N22">
-        <v>57.756968</v>
+        <v>57.5471164</v>
       </c>
       <c r="O22">
-        <v>18.48222976</v>
+        <v>18.415077248</v>
       </c>
       <c r="P22">
-        <v>39.27473824</v>
+        <v>39.132039152</v>
       </c>
       <c r="Q22">
-        <v>39.44573824</v>
+        <v>39.303039152</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1047113948462196</v>
+        <v>0.1052531527778359</v>
       </c>
       <c r="T22">
-        <v>0.7678129636013127</v>
+        <v>0.7748738855861782</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.76138375880861</v>
+        <v>14.05846072267486</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09033283069449033</v>
+        <v>0.09005574551200493</v>
       </c>
       <c r="C23">
-        <v>344.9724691473872</v>
+        <v>343.4049475311833</v>
       </c>
       <c r="D23">
-        <v>415.9844691473872</v>
+        <v>418.5889475311833</v>
       </c>
       <c r="E23">
-        <v>-86.788</v>
+        <v>-82.616</v>
       </c>
       <c r="F23">
-        <v>87.61200000000001</v>
+        <v>91.78400000000001</v>
       </c>
       <c r="G23">
         <v>16.6</v>
@@ -3173,28 +3173,28 @@
         <v>61.954</v>
       </c>
       <c r="M23">
-        <v>4.4068836</v>
+        <v>4.6167352</v>
       </c>
       <c r="N23">
-        <v>57.5471164</v>
+        <v>57.3372648</v>
       </c>
       <c r="O23">
-        <v>18.415077248</v>
+        <v>18.347924736</v>
       </c>
       <c r="P23">
-        <v>39.132039152</v>
+        <v>38.989340064</v>
       </c>
       <c r="Q23">
-        <v>39.303039152</v>
+        <v>39.160340064</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1052531527778359</v>
+        <v>0.1058088019384679</v>
       </c>
       <c r="T23">
-        <v>0.7748738855861782</v>
+        <v>0.7821158568527069</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.05846072267486</v>
+        <v>13.4194397807351</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09005574551200493</v>
+        <v>0.09001326032951956</v>
       </c>
       <c r="C24">
-        <v>343.4049475311833</v>
+        <v>339.6351759054239</v>
       </c>
       <c r="D24">
-        <v>418.5889475311833</v>
+        <v>418.9911759054239</v>
       </c>
       <c r="E24">
-        <v>-82.616</v>
+        <v>-78.44399999999999</v>
       </c>
       <c r="F24">
-        <v>91.78400000000001</v>
+        <v>95.95600000000002</v>
       </c>
       <c r="G24">
         <v>16.6</v>
@@ -3255,45 +3255,45 @@
         <v>61.954</v>
       </c>
       <c r="M24">
-        <v>4.6167352</v>
+        <v>4.970520800000001</v>
       </c>
       <c r="N24">
-        <v>57.3372648</v>
+        <v>56.9834792</v>
       </c>
       <c r="O24">
-        <v>18.347924736</v>
+        <v>18.234713344</v>
       </c>
       <c r="P24">
-        <v>38.989340064</v>
+        <v>38.748765856</v>
       </c>
       <c r="Q24">
-        <v>39.160340064</v>
+        <v>38.919765856</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1058088019384679</v>
+        <v>0.1063788835448306</v>
       </c>
       <c r="T24">
-        <v>0.7821158568527069</v>
+        <v>0.7895459312690155</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.32</v>
       </c>
       <c r="W24">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.4194397807351</v>
+        <v>12.4642874444867</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09001326032951956</v>
+        <v>0.08974637514703418</v>
       </c>
       <c r="C25">
-        <v>339.6351759054239</v>
+        <v>338.0076983163657</v>
       </c>
       <c r="D25">
-        <v>418.9911759054239</v>
+        <v>421.5356983163657</v>
       </c>
       <c r="E25">
-        <v>-78.44399999999999</v>
+        <v>-74.27199999999999</v>
       </c>
       <c r="F25">
-        <v>95.95600000000002</v>
+        <v>100.128</v>
       </c>
       <c r="G25">
         <v>16.6</v>
@@ -3337,28 +3337,28 @@
         <v>61.954</v>
       </c>
       <c r="M25">
-        <v>4.970520800000001</v>
+        <v>5.1866304</v>
       </c>
       <c r="N25">
-        <v>56.9834792</v>
+        <v>56.7673696</v>
       </c>
       <c r="O25">
-        <v>18.234713344</v>
+        <v>18.165558272</v>
       </c>
       <c r="P25">
-        <v>38.748765856</v>
+        <v>38.601811328</v>
       </c>
       <c r="Q25">
-        <v>38.919765856</v>
+        <v>38.772811328</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1063788835448306</v>
+        <v>0.1069639672987292</v>
       </c>
       <c r="T25">
-        <v>0.7895459312690155</v>
+        <v>0.7971715339594376</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.4642874444867</v>
+        <v>11.94494213429976</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08974637514703418</v>
+        <v>0.08947948996454878</v>
       </c>
       <c r="C26">
-        <v>338.0076983163657</v>
+        <v>336.4113151988106</v>
       </c>
       <c r="D26">
-        <v>421.5356983163657</v>
+        <v>424.1113151988106</v>
       </c>
       <c r="E26">
-        <v>-74.27200000000001</v>
+        <v>-70.09999999999999</v>
       </c>
       <c r="F26">
-        <v>100.128</v>
+        <v>104.3</v>
       </c>
       <c r="G26">
         <v>16.6</v>
@@ -3419,28 +3419,28 @@
         <v>61.954</v>
       </c>
       <c r="M26">
-        <v>5.1866304</v>
+        <v>5.402740000000001</v>
       </c>
       <c r="N26">
-        <v>56.7673696</v>
+        <v>56.55126</v>
       </c>
       <c r="O26">
-        <v>18.165558272</v>
+        <v>18.0964032</v>
       </c>
       <c r="P26">
-        <v>38.601811328</v>
+        <v>38.4548568</v>
       </c>
       <c r="Q26">
-        <v>38.772811328</v>
+        <v>38.6258568</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1069639672987292</v>
+        <v>0.107564653286065</v>
       </c>
       <c r="T26">
-        <v>0.7971715339594376</v>
+        <v>0.8050004860549375</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.94494213429976</v>
+        <v>11.46714444892777</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08947948996454878</v>
+        <v>0.0892126047820634</v>
       </c>
       <c r="C27">
-        <v>336.4113151988106</v>
+        <v>334.8466000258595</v>
       </c>
       <c r="D27">
-        <v>424.1113151988106</v>
+        <v>426.7186000258595</v>
       </c>
       <c r="E27">
-        <v>-70.09999999999999</v>
+        <v>-65.92799999999998</v>
       </c>
       <c r="F27">
-        <v>104.3</v>
+        <v>108.472</v>
       </c>
       <c r="G27">
         <v>16.6</v>
@@ -3501,28 +3501,28 @@
         <v>61.954</v>
       </c>
       <c r="M27">
-        <v>5.402740000000001</v>
+        <v>5.618849600000001</v>
       </c>
       <c r="N27">
-        <v>56.55126</v>
+        <v>56.3351504</v>
       </c>
       <c r="O27">
-        <v>18.0964032</v>
+        <v>18.027248128</v>
       </c>
       <c r="P27">
-        <v>38.4548568</v>
+        <v>38.30790227200001</v>
       </c>
       <c r="Q27">
-        <v>38.6258568</v>
+        <v>38.47890227200001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.107564653286065</v>
+        <v>0.1081815740298154</v>
       </c>
       <c r="T27">
-        <v>0.8050004860549375</v>
+        <v>0.8130410314503159</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.46714444892777</v>
+        <v>11.02610043166131</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0892126047820634</v>
+        <v>0.088945719599578</v>
       </c>
       <c r="C28">
-        <v>334.8466000258595</v>
+        <v>333.3141404598759</v>
       </c>
       <c r="D28">
-        <v>426.7186000258595</v>
+        <v>429.3581404598759</v>
       </c>
       <c r="E28">
-        <v>-65.92799999999998</v>
+        <v>-61.75599999999999</v>
       </c>
       <c r="F28">
-        <v>108.472</v>
+        <v>112.644</v>
       </c>
       <c r="G28">
         <v>16.6</v>
@@ -3583,28 +3583,28 @@
         <v>61.954</v>
       </c>
       <c r="M28">
-        <v>5.618849600000001</v>
+        <v>5.834959200000001</v>
       </c>
       <c r="N28">
-        <v>56.3351504</v>
+        <v>56.1190408</v>
       </c>
       <c r="O28">
-        <v>18.027248128</v>
+        <v>17.958093056</v>
       </c>
       <c r="P28">
-        <v>38.30790227200001</v>
+        <v>38.160947744</v>
       </c>
       <c r="Q28">
-        <v>38.47890227200001</v>
+        <v>38.331947744</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1081815740298154</v>
+        <v>0.1088153967117507</v>
       </c>
       <c r="T28">
-        <v>0.8130410314503159</v>
+        <v>0.8213018657606361</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.02610043166131</v>
+        <v>10.61772634159978</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.088945719599578</v>
+        <v>0.08867883441709264</v>
       </c>
       <c r="C29">
-        <v>333.3141404598759</v>
+        <v>331.8145387940651</v>
       </c>
       <c r="D29">
-        <v>429.3581404598759</v>
+        <v>432.0305387940651</v>
       </c>
       <c r="E29">
-        <v>-61.75599999999999</v>
+        <v>-57.58399999999997</v>
       </c>
       <c r="F29">
-        <v>112.644</v>
+        <v>116.816</v>
       </c>
       <c r="G29">
         <v>16.6</v>
@@ -3665,28 +3665,28 @@
         <v>61.954</v>
       </c>
       <c r="M29">
-        <v>5.834959200000001</v>
+        <v>6.051068800000001</v>
       </c>
       <c r="N29">
-        <v>56.1190408</v>
+        <v>55.9029312</v>
       </c>
       <c r="O29">
-        <v>17.958093056</v>
+        <v>17.888937984</v>
       </c>
       <c r="P29">
-        <v>38.160947744</v>
+        <v>38.013993216</v>
       </c>
       <c r="Q29">
-        <v>38.331947744</v>
+        <v>38.184993216</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1088153967117507</v>
+        <v>0.1094668255792953</v>
       </c>
       <c r="T29">
-        <v>0.8213018657606361</v>
+        <v>0.8297921676906875</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.61772634159978</v>
+        <v>10.23852182939979</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08867883441709264</v>
+        <v>0.08841194923460723</v>
       </c>
       <c r="C30">
-        <v>331.8145387940651</v>
+        <v>330.3484124106533</v>
       </c>
       <c r="D30">
-        <v>432.0305387940651</v>
+        <v>434.7364124106533</v>
       </c>
       <c r="E30">
-        <v>-57.58399999999997</v>
+        <v>-53.41199999999998</v>
       </c>
       <c r="F30">
-        <v>116.816</v>
+        <v>120.988</v>
       </c>
       <c r="G30">
         <v>16.6</v>
@@ -3747,28 +3747,28 @@
         <v>61.954</v>
       </c>
       <c r="M30">
-        <v>6.051068800000001</v>
+        <v>6.267178400000001</v>
       </c>
       <c r="N30">
-        <v>55.9029312</v>
+        <v>55.6868216</v>
       </c>
       <c r="O30">
-        <v>17.888937984</v>
+        <v>17.819782912</v>
       </c>
       <c r="P30">
-        <v>38.013993216</v>
+        <v>37.867038688</v>
       </c>
       <c r="Q30">
-        <v>38.184993216</v>
+        <v>38.038038688</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1094668255792953</v>
+        <v>0.1101366045557848</v>
       </c>
       <c r="T30">
-        <v>0.8297921676906875</v>
+        <v>0.8385216330553881</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.23852182939979</v>
+        <v>9.885469352523934</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08841194923460723</v>
+        <v>0.08849186405212184</v>
       </c>
       <c r="C31">
-        <v>330.3484124106533</v>
+        <v>325.3626301634706</v>
       </c>
       <c r="D31">
-        <v>434.7364124106533</v>
+        <v>433.9226301634706</v>
       </c>
       <c r="E31">
-        <v>-53.41200000000001</v>
+        <v>-49.23999999999999</v>
       </c>
       <c r="F31">
-        <v>120.988</v>
+        <v>125.16</v>
       </c>
       <c r="G31">
         <v>16.6</v>
@@ -3829,45 +3829,45 @@
         <v>61.954</v>
       </c>
       <c r="M31">
-        <v>6.2671784</v>
+        <v>6.69606</v>
       </c>
       <c r="N31">
-        <v>55.6868216</v>
+        <v>55.25794</v>
       </c>
       <c r="O31">
-        <v>17.819782912</v>
+        <v>17.6825408</v>
       </c>
       <c r="P31">
-        <v>37.867038688</v>
+        <v>37.5753992</v>
       </c>
       <c r="Q31">
-        <v>38.038038688</v>
+        <v>37.7463992</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1101366045557848</v>
+        <v>0.1108255200744598</v>
       </c>
       <c r="T31">
-        <v>0.8385216330553881</v>
+        <v>0.8475005117162231</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.32</v>
       </c>
       <c r="W31">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>9.885469352523938</v>
+        <v>9.252306580287511</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08849186405212184</v>
+        <v>0.08823653886963646</v>
       </c>
       <c r="C32">
-        <v>325.3626301634706</v>
+        <v>323.8013844257673</v>
       </c>
       <c r="D32">
-        <v>433.9226301634706</v>
+        <v>436.5333844257673</v>
       </c>
       <c r="E32">
-        <v>-49.23999999999999</v>
+        <v>-45.06799999999998</v>
       </c>
       <c r="F32">
-        <v>125.16</v>
+        <v>129.332</v>
       </c>
       <c r="G32">
         <v>16.6</v>
@@ -3911,28 +3911,28 @@
         <v>61.954</v>
       </c>
       <c r="M32">
-        <v>6.69606</v>
+        <v>6.919262000000001</v>
       </c>
       <c r="N32">
-        <v>55.25794</v>
+        <v>55.034738</v>
       </c>
       <c r="O32">
-        <v>17.6825408</v>
+        <v>17.61111616</v>
       </c>
       <c r="P32">
-        <v>37.5753992</v>
+        <v>37.42362184</v>
       </c>
       <c r="Q32">
-        <v>37.7463992</v>
+        <v>37.59462183999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1108255200744598</v>
+        <v>0.1115344041588934</v>
       </c>
       <c r="T32">
-        <v>0.8475005117162231</v>
+        <v>0.856739647729546</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.252306580287511</v>
+        <v>8.953845077697592</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08823653886963646</v>
+        <v>0.08798121368715107</v>
       </c>
       <c r="C33">
-        <v>323.8013844257673</v>
+        <v>322.2717447633843</v>
       </c>
       <c r="D33">
-        <v>436.5333844257673</v>
+        <v>439.1757447633843</v>
       </c>
       <c r="E33">
-        <v>-45.06799999999998</v>
+        <v>-40.89599999999999</v>
       </c>
       <c r="F33">
-        <v>129.332</v>
+        <v>133.504</v>
       </c>
       <c r="G33">
         <v>16.6</v>
@@ -3993,28 +3993,28 @@
         <v>61.954</v>
       </c>
       <c r="M33">
-        <v>6.919262000000001</v>
+        <v>7.142464000000001</v>
       </c>
       <c r="N33">
-        <v>55.034738</v>
+        <v>54.811536</v>
       </c>
       <c r="O33">
-        <v>17.61111616</v>
+        <v>17.53969152</v>
       </c>
       <c r="P33">
-        <v>37.42362184</v>
+        <v>37.27184448</v>
       </c>
       <c r="Q33">
-        <v>37.59462183999999</v>
+        <v>37.44284448</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1115344041588934</v>
+        <v>0.1122641377752222</v>
       </c>
       <c r="T33">
-        <v>0.856739647729546</v>
+        <v>0.8662505230373785</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.953845077697592</v>
+        <v>8.674037419019541</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08798121368715107</v>
+        <v>0.08772588850466567</v>
       </c>
       <c r="C34">
-        <v>322.2717447633843</v>
+        <v>320.7742886114507</v>
       </c>
       <c r="D34">
-        <v>439.1757447633843</v>
+        <v>441.8502886114507</v>
       </c>
       <c r="E34">
-        <v>-40.89599999999999</v>
+        <v>-36.72399999999999</v>
       </c>
       <c r="F34">
-        <v>133.504</v>
+        <v>137.676</v>
       </c>
       <c r="G34">
         <v>16.6</v>
@@ -4075,28 +4075,28 @@
         <v>61.954</v>
       </c>
       <c r="M34">
-        <v>7.142464000000001</v>
+        <v>7.365666000000001</v>
       </c>
       <c r="N34">
-        <v>54.811536</v>
+        <v>54.588334</v>
       </c>
       <c r="O34">
-        <v>17.53969152</v>
+        <v>17.46826688</v>
       </c>
       <c r="P34">
-        <v>37.27184448</v>
+        <v>37.12006712</v>
       </c>
       <c r="Q34">
-        <v>37.44284448</v>
+        <v>37.29106712</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1122641377752222</v>
+        <v>0.1130156544845757</v>
       </c>
       <c r="T34">
-        <v>0.8662505230373785</v>
+        <v>0.8760453050708179</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.674037419019541</v>
+        <v>8.411187800261374</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08772588850466567</v>
+        <v>0.0874705633221803</v>
       </c>
       <c r="C35">
-        <v>320.7742886114507</v>
+        <v>319.3096075574099</v>
       </c>
       <c r="D35">
-        <v>441.8502886114507</v>
+        <v>444.5576075574099</v>
       </c>
       <c r="E35">
-        <v>-36.72399999999999</v>
+        <v>-32.55199999999999</v>
       </c>
       <c r="F35">
-        <v>137.676</v>
+        <v>141.848</v>
       </c>
       <c r="G35">
         <v>16.6</v>
@@ -4157,28 +4157,28 @@
         <v>61.954</v>
       </c>
       <c r="M35">
-        <v>7.365666000000001</v>
+        <v>7.588868000000001</v>
       </c>
       <c r="N35">
-        <v>54.588334</v>
+        <v>54.365132</v>
       </c>
       <c r="O35">
-        <v>17.46826688</v>
+        <v>17.39684224</v>
       </c>
       <c r="P35">
-        <v>37.12006712</v>
+        <v>36.96828976</v>
       </c>
       <c r="Q35">
-        <v>37.29106712</v>
+        <v>37.13928976</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1130156544845757</v>
+        <v>0.1137899444275459</v>
       </c>
       <c r="T35">
-        <v>0.8760453050708179</v>
+        <v>0.8861368986810282</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.411187800261374</v>
+        <v>8.163799923783099</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0874705633221803</v>
+        <v>0.0872152381396949</v>
       </c>
       <c r="C36">
-        <v>319.3096075574099</v>
+        <v>317.8783077772665</v>
       </c>
       <c r="D36">
-        <v>444.5576075574099</v>
+        <v>447.2983077772665</v>
       </c>
       <c r="E36">
-        <v>-32.55199999999999</v>
+        <v>-28.37999999999997</v>
       </c>
       <c r="F36">
-        <v>141.848</v>
+        <v>146.02</v>
       </c>
       <c r="G36">
         <v>16.6</v>
@@ -4239,28 +4239,28 @@
         <v>61.954</v>
       </c>
       <c r="M36">
-        <v>7.588868000000001</v>
+        <v>7.812070000000002</v>
       </c>
       <c r="N36">
-        <v>54.365132</v>
+        <v>54.14193</v>
       </c>
       <c r="O36">
-        <v>17.39684224</v>
+        <v>17.3254176</v>
       </c>
       <c r="P36">
-        <v>36.96828976</v>
+        <v>36.8165124</v>
       </c>
       <c r="Q36">
-        <v>37.13928976</v>
+        <v>36.9875124</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1137899444275459</v>
+        <v>0.1145880586764537</v>
       </c>
       <c r="T36">
-        <v>0.8861368986810282</v>
+        <v>0.8965390028638603</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.163799923783099</v>
+        <v>7.930548497389295</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0872152381396949</v>
+        <v>0.08695991295720952</v>
       </c>
       <c r="C37">
-        <v>317.8783077772665</v>
+        <v>316.4810104880656</v>
       </c>
       <c r="D37">
-        <v>447.2983077772665</v>
+        <v>450.0730104880657</v>
       </c>
       <c r="E37">
-        <v>-28.37999999999997</v>
+        <v>-24.20799999999997</v>
       </c>
       <c r="F37">
-        <v>146.02</v>
+        <v>150.192</v>
       </c>
       <c r="G37">
         <v>16.6</v>
@@ -4321,28 +4321,28 @@
         <v>61.954</v>
       </c>
       <c r="M37">
-        <v>7.812070000000002</v>
+        <v>8.035272000000003</v>
       </c>
       <c r="N37">
-        <v>54.14193</v>
+        <v>53.918728</v>
       </c>
       <c r="O37">
-        <v>17.3254176</v>
+        <v>17.25399296</v>
       </c>
       <c r="P37">
-        <v>36.8165124</v>
+        <v>36.66473504</v>
       </c>
       <c r="Q37">
-        <v>36.9875124</v>
+        <v>36.83573504</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1145880586764537</v>
+        <v>0.1154111139956399</v>
       </c>
       <c r="T37">
-        <v>0.8965390028638603</v>
+        <v>0.907266172802406</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.930548497389295</v>
+        <v>7.710255483572925</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08695991295720951</v>
+        <v>0.08690586777472413</v>
       </c>
       <c r="C38">
-        <v>316.4810104880659</v>
+        <v>312.900757586482</v>
       </c>
       <c r="D38">
-        <v>450.0730104880658</v>
+        <v>450.6647575864819</v>
       </c>
       <c r="E38">
-        <v>-24.208</v>
+        <v>-20.036</v>
       </c>
       <c r="F38">
-        <v>150.192</v>
+        <v>154.364</v>
       </c>
       <c r="G38">
         <v>16.6</v>
@@ -4403,45 +4403,45 @@
         <v>61.954</v>
       </c>
       <c r="M38">
-        <v>8.035272000000001</v>
+        <v>8.3819652</v>
       </c>
       <c r="N38">
-        <v>53.918728</v>
+        <v>53.5720348</v>
       </c>
       <c r="O38">
-        <v>17.25399296</v>
+        <v>17.143051136</v>
       </c>
       <c r="P38">
-        <v>36.66473504</v>
+        <v>36.428983664</v>
       </c>
       <c r="Q38">
-        <v>36.83573504</v>
+        <v>36.599983664</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1154111139956399</v>
+        <v>0.1162602980551177</v>
       </c>
       <c r="T38">
-        <v>0.9072661728024057</v>
+        <v>0.9183338878183657</v>
       </c>
       <c r="U38">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.32</v>
       </c>
       <c r="W38">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>7.710255483572927</v>
+        <v>7.391345409069462</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08690586777472413</v>
+        <v>0.08665598259223874</v>
       </c>
       <c r="C39">
-        <v>312.900757586482</v>
+        <v>311.4851334718247</v>
       </c>
       <c r="D39">
-        <v>450.6647575864819</v>
+        <v>453.4211334718248</v>
       </c>
       <c r="E39">
-        <v>-20.036</v>
+        <v>-15.86399999999998</v>
       </c>
       <c r="F39">
-        <v>154.364</v>
+        <v>158.536</v>
       </c>
       <c r="G39">
         <v>16.6</v>
@@ -4485,28 +4485,28 @@
         <v>61.954</v>
       </c>
       <c r="M39">
-        <v>8.3819652</v>
+        <v>8.608504800000002</v>
       </c>
       <c r="N39">
-        <v>53.5720348</v>
+        <v>53.3454952</v>
       </c>
       <c r="O39">
-        <v>17.143051136</v>
+        <v>17.070558464</v>
       </c>
       <c r="P39">
-        <v>36.428983664</v>
+        <v>36.274936736</v>
       </c>
       <c r="Q39">
-        <v>36.599983664</v>
+        <v>36.445936736</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1162602980551177</v>
+        <v>0.1171368751487722</v>
       </c>
       <c r="T39">
-        <v>0.9183338878183657</v>
+        <v>0.9297586258993563</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.391345409069462</v>
+        <v>7.196836319357107</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08665598259223874</v>
+        <v>0.08640609740975336</v>
       </c>
       <c r="C40">
-        <v>311.4851334718247</v>
+        <v>310.1034341879217</v>
       </c>
       <c r="D40">
-        <v>453.4211334718248</v>
+        <v>456.2114341879217</v>
       </c>
       <c r="E40">
-        <v>-15.86399999999998</v>
+        <v>-11.69199999999998</v>
       </c>
       <c r="F40">
-        <v>158.536</v>
+        <v>162.708</v>
       </c>
       <c r="G40">
         <v>16.6</v>
@@ -4567,28 +4567,28 @@
         <v>61.954</v>
       </c>
       <c r="M40">
-        <v>8.608504800000002</v>
+        <v>8.835044400000001</v>
       </c>
       <c r="N40">
-        <v>53.3454952</v>
+        <v>53.1189556</v>
       </c>
       <c r="O40">
-        <v>17.070558464</v>
+        <v>16.998065792</v>
       </c>
       <c r="P40">
-        <v>36.274936736</v>
+        <v>36.120889808</v>
       </c>
       <c r="Q40">
-        <v>36.445936736</v>
+        <v>36.291889808</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1171368751487722</v>
+        <v>0.1180421924750055</v>
       </c>
       <c r="T40">
-        <v>0.9297586258993563</v>
+        <v>0.941557945556773</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.196836319357107</v>
+        <v>7.012302054758208</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08640609740975336</v>
+        <v>0.08615621222726796</v>
       </c>
       <c r="C41">
-        <v>310.1034341879217</v>
+        <v>308.7562899212094</v>
       </c>
       <c r="D41">
-        <v>456.2114341879217</v>
+        <v>459.0362899212093</v>
       </c>
       <c r="E41">
-        <v>-11.69199999999998</v>
+        <v>-7.519999999999982</v>
       </c>
       <c r="F41">
-        <v>162.708</v>
+        <v>166.88</v>
       </c>
       <c r="G41">
         <v>16.6</v>
@@ -4649,28 +4649,28 @@
         <v>61.954</v>
       </c>
       <c r="M41">
-        <v>8.835044400000001</v>
+        <v>9.061584000000002</v>
       </c>
       <c r="N41">
-        <v>53.1189556</v>
+        <v>52.892416</v>
       </c>
       <c r="O41">
-        <v>16.998065792</v>
+        <v>16.92557312</v>
       </c>
       <c r="P41">
-        <v>36.120889808</v>
+        <v>35.96684288</v>
       </c>
       <c r="Q41">
-        <v>36.291889808</v>
+        <v>36.13784288</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1180421924750055</v>
+        <v>0.1189776870454466</v>
       </c>
       <c r="T41">
-        <v>0.941557945556773</v>
+        <v>0.9537505758694369</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.012302054758208</v>
+        <v>6.836994503389252</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08615621222726796</v>
+        <v>0.08590632704478258</v>
       </c>
       <c r="C42">
-        <v>308.7562899212094</v>
+        <v>307.4443465638008</v>
       </c>
       <c r="D42">
-        <v>459.0362899212093</v>
+        <v>461.8963465638008</v>
       </c>
       <c r="E42">
-        <v>-7.519999999999982</v>
+        <v>-3.347999999999985</v>
       </c>
       <c r="F42">
-        <v>166.88</v>
+        <v>171.052</v>
       </c>
       <c r="G42">
         <v>16.6</v>
@@ -4731,28 +4731,28 @@
         <v>61.954</v>
       </c>
       <c r="M42">
-        <v>9.061584000000002</v>
+        <v>9.2881236</v>
       </c>
       <c r="N42">
-        <v>52.892416</v>
+        <v>52.6658764</v>
       </c>
       <c r="O42">
-        <v>16.92557312</v>
+        <v>16.853080448</v>
       </c>
       <c r="P42">
-        <v>35.96684288</v>
+        <v>35.812795952</v>
       </c>
       <c r="Q42">
-        <v>36.13784288</v>
+        <v>35.983795952</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1189776870454466</v>
+        <v>0.1199448932962417</v>
       </c>
       <c r="T42">
-        <v>0.9537505758694369</v>
+        <v>0.9663565156842249</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.836994503389252</v>
+        <v>6.670238539891954</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08590632704478258</v>
+        <v>0.08565644186229721</v>
       </c>
       <c r="C43">
-        <v>307.4443465638008</v>
+        <v>306.16826620583</v>
       </c>
       <c r="D43">
-        <v>461.8963465638008</v>
+        <v>464.7922662058301</v>
       </c>
       <c r="E43">
-        <v>-3.347999999999985</v>
+        <v>0.8240000000000407</v>
       </c>
       <c r="F43">
-        <v>171.052</v>
+        <v>175.224</v>
       </c>
       <c r="G43">
         <v>16.6</v>
@@ -4813,28 +4813,28 @@
         <v>61.954</v>
       </c>
       <c r="M43">
-        <v>9.2881236</v>
+        <v>9.514663200000003</v>
       </c>
       <c r="N43">
-        <v>52.6658764</v>
+        <v>52.4393368</v>
       </c>
       <c r="O43">
-        <v>16.853080448</v>
+        <v>16.780587776</v>
       </c>
       <c r="P43">
-        <v>35.812795952</v>
+        <v>35.658749024</v>
       </c>
       <c r="Q43">
-        <v>35.983795952</v>
+        <v>35.829749024</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1199448932962417</v>
+        <v>0.1209454514867193</v>
       </c>
       <c r="T43">
-        <v>0.9663565156842249</v>
+        <v>0.9793971430788333</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.670238539891954</v>
+        <v>6.511423336561191</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08565644186229721</v>
+        <v>0.08540655667981183</v>
       </c>
       <c r="C44">
-        <v>306.16826620583</v>
+        <v>304.9287276464339</v>
       </c>
       <c r="D44">
-        <v>464.7922662058301</v>
+        <v>467.7247276464338</v>
       </c>
       <c r="E44">
-        <v>0.8240000000000123</v>
+        <v>4.996000000000009</v>
       </c>
       <c r="F44">
-        <v>175.224</v>
+        <v>179.396</v>
       </c>
       <c r="G44">
         <v>16.6</v>
@@ -4895,28 +4895,28 @@
         <v>61.954</v>
       </c>
       <c r="M44">
-        <v>9.514663200000001</v>
+        <v>9.741202800000002</v>
       </c>
       <c r="N44">
-        <v>52.4393368</v>
+        <v>52.2127972</v>
       </c>
       <c r="O44">
-        <v>16.780587776</v>
+        <v>16.708095104</v>
       </c>
       <c r="P44">
-        <v>35.658749024</v>
+        <v>35.504702096</v>
       </c>
       <c r="Q44">
-        <v>35.829749024</v>
+        <v>35.675702096</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1209454514867193</v>
+        <v>0.121981116982126</v>
       </c>
       <c r="T44">
-        <v>0.9793971430788333</v>
+        <v>0.9928953363469367</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.511423336561193</v>
+        <v>6.359994886873722</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08540655667981183</v>
+        <v>0.08515667149732645</v>
       </c>
       <c r="C45">
-        <v>304.9287276464339</v>
+        <v>303.726426924199</v>
       </c>
       <c r="D45">
-        <v>467.7247276464338</v>
+        <v>470.694426924199</v>
       </c>
       <c r="E45">
-        <v>4.996000000000009</v>
+        <v>9.168000000000006</v>
       </c>
       <c r="F45">
-        <v>179.396</v>
+        <v>183.568</v>
       </c>
       <c r="G45">
         <v>16.6</v>
@@ -4977,28 +4977,28 @@
         <v>61.954</v>
       </c>
       <c r="M45">
-        <v>9.741202800000002</v>
+        <v>9.967742400000001</v>
       </c>
       <c r="N45">
-        <v>52.2127972</v>
+        <v>51.9862576</v>
       </c>
       <c r="O45">
-        <v>16.708095104</v>
+        <v>16.635602432</v>
       </c>
       <c r="P45">
-        <v>35.504702096</v>
+        <v>35.350655168</v>
       </c>
       <c r="Q45">
-        <v>35.675702096</v>
+        <v>35.521655168</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.121981116982126</v>
+        <v>0.12305377053094</v>
       </c>
       <c r="T45">
-        <v>0.9928953363469367</v>
+        <v>1.006875607946044</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.359994886873722</v>
+        <v>6.215449548535684</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08515667149732645</v>
+        <v>0.08521278631484104</v>
       </c>
       <c r="C46">
-        <v>303.726426924199</v>
+        <v>298.8842654273438</v>
       </c>
       <c r="D46">
-        <v>470.694426924199</v>
+        <v>470.0242654273439</v>
       </c>
       <c r="E46">
-        <v>9.168000000000006</v>
+        <v>13.34000000000003</v>
       </c>
       <c r="F46">
-        <v>183.568</v>
+        <v>187.74</v>
       </c>
       <c r="G46">
         <v>16.6</v>
@@ -5059,45 +5059,45 @@
         <v>61.954</v>
       </c>
       <c r="M46">
-        <v>9.967742400000001</v>
+        <v>10.382022</v>
       </c>
       <c r="N46">
-        <v>51.9862576</v>
+        <v>51.571978</v>
       </c>
       <c r="O46">
-        <v>16.635602432</v>
+        <v>16.50303296</v>
       </c>
       <c r="P46">
-        <v>35.350655168</v>
+        <v>35.06894504</v>
       </c>
       <c r="Q46">
-        <v>35.521655168</v>
+        <v>35.23994504</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.12305377053094</v>
+        <v>0.1241654296633473</v>
       </c>
       <c r="T46">
-        <v>1.006875607946044</v>
+        <v>1.021364253057846</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.32</v>
       </c>
       <c r="W46">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>6.215449548535684</v>
+        <v>5.967431007177598</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08521278631484104</v>
+        <v>0.08496970113235566</v>
       </c>
       <c r="C47">
-        <v>298.8842654273438</v>
+        <v>297.6292122262966</v>
       </c>
       <c r="D47">
-        <v>470.0242654273439</v>
+        <v>472.9412122262966</v>
       </c>
       <c r="E47">
-        <v>13.34000000000003</v>
+        <v>17.51200000000003</v>
       </c>
       <c r="F47">
-        <v>187.74</v>
+        <v>191.912</v>
       </c>
       <c r="G47">
         <v>16.6</v>
@@ -5141,28 +5141,28 @@
         <v>61.954</v>
       </c>
       <c r="M47">
-        <v>10.382022</v>
+        <v>10.6127336</v>
       </c>
       <c r="N47">
-        <v>51.571978</v>
+        <v>51.34126639999999</v>
       </c>
       <c r="O47">
-        <v>16.50303296</v>
+        <v>16.429205248</v>
       </c>
       <c r="P47">
-        <v>35.06894504</v>
+        <v>34.91206115199999</v>
       </c>
       <c r="Q47">
-        <v>35.23994504</v>
+        <v>35.08306115199999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1241654296633473</v>
+        <v>0.1253182613562142</v>
       </c>
       <c r="T47">
-        <v>1.021364253057846</v>
+        <v>1.03638951465527</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.967431007177598</v>
+        <v>5.837704246151999</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08496970113235566</v>
+        <v>0.08472661594987027</v>
       </c>
       <c r="C48">
-        <v>297.6292122262966</v>
+        <v>296.4105899621611</v>
       </c>
       <c r="D48">
-        <v>472.9412122262966</v>
+        <v>475.8945899621611</v>
       </c>
       <c r="E48">
-        <v>17.51200000000003</v>
+        <v>21.68400000000003</v>
       </c>
       <c r="F48">
-        <v>191.912</v>
+        <v>196.084</v>
       </c>
       <c r="G48">
         <v>16.6</v>
@@ -5223,28 +5223,28 @@
         <v>61.954</v>
       </c>
       <c r="M48">
-        <v>10.6127336</v>
+        <v>10.8434452</v>
       </c>
       <c r="N48">
-        <v>51.34126639999999</v>
+        <v>51.1105548</v>
       </c>
       <c r="O48">
-        <v>16.429205248</v>
+        <v>16.355377536</v>
       </c>
       <c r="P48">
-        <v>34.91206115199999</v>
+        <v>34.755177264</v>
       </c>
       <c r="Q48">
-        <v>35.08306115199999</v>
+        <v>34.926177264</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1253182613562142</v>
+        <v>0.1265145961318307</v>
       </c>
       <c r="T48">
-        <v>1.03638951465527</v>
+        <v>1.05198176725637</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.837704246151999</v>
+        <v>5.713497772829617</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08472661594987027</v>
+        <v>0.08448353076738488</v>
       </c>
       <c r="C49">
-        <v>296.4105899621611</v>
+        <v>295.2290854249563</v>
       </c>
       <c r="D49">
-        <v>475.8945899621611</v>
+        <v>478.8850854249563</v>
       </c>
       <c r="E49">
-        <v>21.68400000000003</v>
+        <v>25.85600000000002</v>
       </c>
       <c r="F49">
-        <v>196.084</v>
+        <v>200.256</v>
       </c>
       <c r="G49">
         <v>16.6</v>
@@ -5305,28 +5305,28 @@
         <v>61.954</v>
       </c>
       <c r="M49">
-        <v>10.8434452</v>
+        <v>11.0741568</v>
       </c>
       <c r="N49">
-        <v>51.1105548</v>
+        <v>50.8798432</v>
       </c>
       <c r="O49">
-        <v>16.355377536</v>
+        <v>16.281549824</v>
       </c>
       <c r="P49">
-        <v>34.755177264</v>
+        <v>34.598293376</v>
       </c>
       <c r="Q49">
-        <v>34.926177264</v>
+        <v>34.769293376</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1265145961318307</v>
+        <v>0.1277569437834325</v>
       </c>
       <c r="T49">
-        <v>1.05198176725637</v>
+        <v>1.06817372188059</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.713497772829617</v>
+        <v>5.594466569228999</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08448353076738488</v>
+        <v>0.08424044558489949</v>
       </c>
       <c r="C50">
-        <v>295.2290854249563</v>
+        <v>294.0854027768702</v>
       </c>
       <c r="D50">
-        <v>478.8850854249563</v>
+        <v>481.9134027768702</v>
       </c>
       <c r="E50">
-        <v>25.85599999999999</v>
+        <v>30.02800000000002</v>
       </c>
       <c r="F50">
-        <v>200.256</v>
+        <v>204.428</v>
       </c>
       <c r="G50">
         <v>16.6</v>
@@ -5387,28 +5387,28 @@
         <v>61.954</v>
       </c>
       <c r="M50">
-        <v>11.0741568</v>
+        <v>11.3048684</v>
       </c>
       <c r="N50">
-        <v>50.8798432</v>
+        <v>50.6491316</v>
       </c>
       <c r="O50">
-        <v>16.281549824</v>
+        <v>16.207722112</v>
       </c>
       <c r="P50">
-        <v>34.598293376</v>
+        <v>34.441409488</v>
       </c>
       <c r="Q50">
-        <v>34.769293376</v>
+        <v>34.612409488</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1277569437834325</v>
+        <v>0.1290480109507833</v>
       </c>
       <c r="T50">
-        <v>1.06817372188059</v>
+        <v>1.085000655117525</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.594466569229</v>
+        <v>5.480293782101876</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08424044558489949</v>
+        <v>0.08399736040241411</v>
       </c>
       <c r="C51">
-        <v>294.0854027768702</v>
+        <v>292.9802641050358</v>
       </c>
       <c r="D51">
-        <v>481.9134027768702</v>
+        <v>484.9802641050358</v>
       </c>
       <c r="E51">
-        <v>30.02800000000002</v>
+        <v>34.20000000000002</v>
       </c>
       <c r="F51">
-        <v>204.428</v>
+        <v>208.6</v>
       </c>
       <c r="G51">
         <v>16.6</v>
@@ -5469,28 +5469,28 @@
         <v>61.954</v>
       </c>
       <c r="M51">
-        <v>11.3048684</v>
+        <v>11.53558</v>
       </c>
       <c r="N51">
-        <v>50.6491316</v>
+        <v>50.41842</v>
       </c>
       <c r="O51">
-        <v>16.207722112</v>
+        <v>16.1338944</v>
       </c>
       <c r="P51">
-        <v>34.441409488</v>
+        <v>34.28452559999999</v>
       </c>
       <c r="Q51">
-        <v>34.612409488</v>
+        <v>34.45552559999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1290480109507833</v>
+        <v>0.1303907208048282</v>
       </c>
       <c r="T51">
-        <v>1.085000655117525</v>
+        <v>1.102500665683936</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.480293782101876</v>
+        <v>5.370687906459839</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08399736040241411</v>
+        <v>0.08375427521992873</v>
       </c>
       <c r="C52">
-        <v>292.9802641050358</v>
+        <v>291.9144099955488</v>
       </c>
       <c r="D52">
-        <v>484.9802641050358</v>
+        <v>488.0864099955488</v>
       </c>
       <c r="E52">
-        <v>34.20000000000002</v>
+        <v>38.37200000000001</v>
       </c>
       <c r="F52">
-        <v>208.6</v>
+        <v>212.772</v>
       </c>
       <c r="G52">
         <v>16.6</v>
@@ -5551,28 +5551,28 @@
         <v>61.954</v>
       </c>
       <c r="M52">
-        <v>11.53558</v>
+        <v>11.7662916</v>
       </c>
       <c r="N52">
-        <v>50.41842</v>
+        <v>50.1877084</v>
       </c>
       <c r="O52">
-        <v>16.1338944</v>
+        <v>16.060066688</v>
       </c>
       <c r="P52">
-        <v>34.28452559999999</v>
+        <v>34.127641712</v>
       </c>
       <c r="Q52">
-        <v>34.45552559999999</v>
+        <v>34.298641712</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1303907208048282</v>
+        <v>0.1317882351427117</v>
       </c>
       <c r="T52">
-        <v>1.102500665683936</v>
+        <v>1.120714962395916</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.370687906459839</v>
+        <v>5.265380300450823</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08375427521992873</v>
+        <v>0.08351119003744333</v>
       </c>
       <c r="C53">
-        <v>291.9144099955488</v>
+        <v>290.8886001296869</v>
       </c>
       <c r="D53">
-        <v>488.0864099955488</v>
+        <v>491.2326001296869</v>
       </c>
       <c r="E53">
-        <v>38.37200000000001</v>
+        <v>42.54400000000004</v>
       </c>
       <c r="F53">
-        <v>212.772</v>
+        <v>216.944</v>
       </c>
       <c r="G53">
         <v>16.6</v>
@@ -5633,28 +5633,28 @@
         <v>61.954</v>
       </c>
       <c r="M53">
-        <v>11.7662916</v>
+        <v>11.9970032</v>
       </c>
       <c r="N53">
-        <v>50.1877084</v>
+        <v>49.9569968</v>
       </c>
       <c r="O53">
-        <v>16.060066688</v>
+        <v>15.986238976</v>
       </c>
       <c r="P53">
-        <v>34.127641712</v>
+        <v>33.970757824</v>
       </c>
       <c r="Q53">
-        <v>34.298641712</v>
+        <v>34.141757824</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1317882351427117</v>
+        <v>0.1332439792446736</v>
       </c>
       <c r="T53">
-        <v>1.120714962395916</v>
+        <v>1.139688188137561</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.265380300450823</v>
+        <v>5.164122986980614</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08351119003744333</v>
+        <v>0.08326810485495793</v>
       </c>
       <c r="C54">
-        <v>290.8886001296869</v>
+        <v>289.9036139033365</v>
       </c>
       <c r="D54">
-        <v>491.2326001296869</v>
+        <v>494.4196139033365</v>
       </c>
       <c r="E54">
-        <v>42.54400000000004</v>
+        <v>46.71600000000004</v>
       </c>
       <c r="F54">
-        <v>216.944</v>
+        <v>221.116</v>
       </c>
       <c r="G54">
         <v>16.6</v>
@@ -5715,28 +5715,28 @@
         <v>61.954</v>
       </c>
       <c r="M54">
-        <v>11.9970032</v>
+        <v>12.2277148</v>
       </c>
       <c r="N54">
-        <v>49.9569968</v>
+        <v>49.7262852</v>
       </c>
       <c r="O54">
-        <v>15.986238976</v>
+        <v>15.912411264</v>
       </c>
       <c r="P54">
-        <v>33.970757824</v>
+        <v>33.813873936</v>
       </c>
       <c r="Q54">
-        <v>34.141757824</v>
+        <v>33.984873936</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1332439792446736</v>
+        <v>0.1347616699041658</v>
       </c>
       <c r="T54">
-        <v>1.139688188137561</v>
+        <v>1.159468785187362</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.164122986980614</v>
+        <v>5.066686704207395</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08326810485495793</v>
+        <v>0.08302501967247256</v>
       </c>
       <c r="C55">
-        <v>289.9036139033365</v>
+        <v>288.9602510706909</v>
       </c>
       <c r="D55">
-        <v>494.4196139033365</v>
+        <v>497.6482510706909</v>
       </c>
       <c r="E55">
-        <v>46.71600000000004</v>
+        <v>50.88800000000003</v>
       </c>
       <c r="F55">
-        <v>221.116</v>
+        <v>225.288</v>
       </c>
       <c r="G55">
         <v>16.6</v>
@@ -5797,28 +5797,28 @@
         <v>61.954</v>
       </c>
       <c r="M55">
-        <v>12.2277148</v>
+        <v>12.4584264</v>
       </c>
       <c r="N55">
-        <v>49.7262852</v>
+        <v>49.4955736</v>
       </c>
       <c r="O55">
-        <v>15.912411264</v>
+        <v>15.838583552</v>
       </c>
       <c r="P55">
-        <v>33.813873936</v>
+        <v>33.656990048</v>
       </c>
       <c r="Q55">
-        <v>33.984873936</v>
+        <v>33.827990048</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1347616699041658</v>
+        <v>0.1363453471140708</v>
       </c>
       <c r="T55">
-        <v>1.159468785187362</v>
+        <v>1.180109408195849</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.066686704207395</v>
+        <v>4.972859172647999</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08302501967247256</v>
+        <v>0.08278193448998716</v>
       </c>
       <c r="C56">
-        <v>288.9602510706909</v>
+        <v>288.0593324133342</v>
       </c>
       <c r="D56">
-        <v>497.6482510706909</v>
+        <v>500.9193324133342</v>
       </c>
       <c r="E56">
-        <v>50.88800000000003</v>
+        <v>55.06000000000003</v>
       </c>
       <c r="F56">
-        <v>225.288</v>
+        <v>229.46</v>
       </c>
       <c r="G56">
         <v>16.6</v>
@@ -5879,28 +5879,28 @@
         <v>61.954</v>
       </c>
       <c r="M56">
-        <v>12.4584264</v>
+        <v>12.689138</v>
       </c>
       <c r="N56">
-        <v>49.4955736</v>
+        <v>49.264862</v>
       </c>
       <c r="O56">
-        <v>15.838583552</v>
+        <v>15.76475584</v>
       </c>
       <c r="P56">
-        <v>33.656990048</v>
+        <v>33.50010616</v>
       </c>
       <c r="Q56">
-        <v>33.827990048</v>
+        <v>33.67110616</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1363453471140708</v>
+        <v>0.1379994099777493</v>
       </c>
       <c r="T56">
-        <v>1.180109408195849</v>
+        <v>1.201667392226936</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.972859172647999</v>
+        <v>4.882443551327126</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08278193448998716</v>
+        <v>0.08253884930750177</v>
       </c>
       <c r="C57">
-        <v>288.0593324133342</v>
+        <v>287.2017004358867</v>
       </c>
       <c r="D57">
-        <v>500.9193324133342</v>
+        <v>504.2337004358867</v>
       </c>
       <c r="E57">
-        <v>55.06000000000003</v>
+        <v>59.23200000000006</v>
       </c>
       <c r="F57">
-        <v>229.46</v>
+        <v>233.6320000000001</v>
       </c>
       <c r="G57">
         <v>16.6</v>
@@ -5961,28 +5961,28 @@
         <v>61.954</v>
       </c>
       <c r="M57">
-        <v>12.689138</v>
+        <v>12.9198496</v>
       </c>
       <c r="N57">
-        <v>49.264862</v>
+        <v>49.03415039999999</v>
       </c>
       <c r="O57">
-        <v>15.76475584</v>
+        <v>15.690928128</v>
       </c>
       <c r="P57">
-        <v>33.50010616</v>
+        <v>33.343222272</v>
       </c>
       <c r="Q57">
-        <v>33.67110616</v>
+        <v>33.514222272</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1379994099777493</v>
+        <v>0.1397286575170495</v>
       </c>
       <c r="T57">
-        <v>1.201667392226936</v>
+        <v>1.224205284623072</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.882443551327126</v>
+        <v>4.795257059339141</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08253884930750177</v>
+        <v>0.08229576412501639</v>
       </c>
       <c r="C58">
-        <v>287.2017004358867</v>
+        <v>286.3882200894515</v>
       </c>
       <c r="D58">
-        <v>504.2337004358867</v>
+        <v>507.5922200894515</v>
       </c>
       <c r="E58">
-        <v>59.23200000000006</v>
+        <v>63.40400000000005</v>
       </c>
       <c r="F58">
-        <v>233.6320000000001</v>
+        <v>237.8040000000001</v>
       </c>
       <c r="G58">
         <v>16.6</v>
@@ -6043,28 +6043,28 @@
         <v>61.954</v>
       </c>
       <c r="M58">
-        <v>12.9198496</v>
+        <v>13.1505612</v>
       </c>
       <c r="N58">
-        <v>49.03415039999999</v>
+        <v>48.8034388</v>
       </c>
       <c r="O58">
-        <v>15.690928128</v>
+        <v>15.617100416</v>
       </c>
       <c r="P58">
-        <v>33.343222272</v>
+        <v>33.186338384</v>
       </c>
       <c r="Q58">
-        <v>33.514222272</v>
+        <v>33.35733838399999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1397286575170495</v>
+        <v>0.1415383351744567</v>
       </c>
       <c r="T58">
-        <v>1.224205284623072</v>
+        <v>1.247791451084145</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.795257059339141</v>
+        <v>4.71112974250863</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08229576412501639</v>
+        <v>0.08205267894253102</v>
       </c>
       <c r="C59">
-        <v>286.3882200894515</v>
+        <v>285.6197795241681</v>
       </c>
       <c r="D59">
-        <v>507.5922200894515</v>
+        <v>510.9957795241681</v>
       </c>
       <c r="E59">
-        <v>63.40400000000005</v>
+        <v>67.57600000000005</v>
       </c>
       <c r="F59">
-        <v>237.8040000000001</v>
+        <v>241.9760000000001</v>
       </c>
       <c r="G59">
         <v>16.6</v>
@@ -6125,28 +6125,28 @@
         <v>61.954</v>
       </c>
       <c r="M59">
-        <v>13.1505612</v>
+        <v>13.3812728</v>
       </c>
       <c r="N59">
-        <v>48.8034388</v>
+        <v>48.5727272</v>
       </c>
       <c r="O59">
-        <v>15.617100416</v>
+        <v>15.543272704</v>
       </c>
       <c r="P59">
-        <v>33.186338384</v>
+        <v>33.029454496</v>
       </c>
       <c r="Q59">
-        <v>33.35733838399999</v>
+        <v>33.200454496</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1415383351744567</v>
+        <v>0.1434341879584072</v>
       </c>
       <c r="T59">
-        <v>1.247791451084145</v>
+        <v>1.272500768329079</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.71112974250863</v>
+        <v>4.629903367637792</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.082052678942531</v>
+        <v>0.08180959376004562</v>
       </c>
       <c r="C60">
-        <v>285.6197795241683</v>
+        <v>284.8972908722445</v>
       </c>
       <c r="D60">
-        <v>510.9957795241683</v>
+        <v>514.4452908722445</v>
       </c>
       <c r="E60">
-        <v>67.57599999999999</v>
+        <v>71.74800000000002</v>
       </c>
       <c r="F60">
-        <v>241.976</v>
+        <v>246.148</v>
       </c>
       <c r="G60">
         <v>16.6</v>
@@ -6207,28 +6207,28 @@
         <v>61.954</v>
       </c>
       <c r="M60">
-        <v>13.3812728</v>
+        <v>13.6119844</v>
       </c>
       <c r="N60">
-        <v>48.5727272</v>
+        <v>48.3420156</v>
       </c>
       <c r="O60">
-        <v>15.543272704</v>
+        <v>15.469444992</v>
       </c>
       <c r="P60">
-        <v>33.029454496</v>
+        <v>32.872570608</v>
       </c>
       <c r="Q60">
-        <v>33.200454496</v>
+        <v>33.043570608</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1434341879584071</v>
+        <v>0.1454225213659649</v>
       </c>
       <c r="T60">
-        <v>1.272500768329078</v>
+        <v>1.298415418122545</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.629903367637793</v>
+        <v>4.551430429203253</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08180959376004562</v>
+        <v>0.08258650857756022</v>
       </c>
       <c r="C61">
-        <v>284.8972908722445</v>
+        <v>269.8604334901808</v>
       </c>
       <c r="D61">
-        <v>514.4452908722445</v>
+        <v>503.5804334901808</v>
       </c>
       <c r="E61">
-        <v>71.74800000000002</v>
+        <v>75.92000000000002</v>
       </c>
       <c r="F61">
-        <v>246.148</v>
+        <v>250.32</v>
       </c>
       <c r="G61">
         <v>16.6</v>
@@ -6289,45 +6289,45 @@
         <v>61.954</v>
       </c>
       <c r="M61">
-        <v>13.6119844</v>
+        <v>14.468496</v>
       </c>
       <c r="N61">
-        <v>48.3420156</v>
+        <v>47.485504</v>
       </c>
       <c r="O61">
-        <v>15.469444992</v>
+        <v>15.19536128</v>
       </c>
       <c r="P61">
-        <v>32.872570608</v>
+        <v>32.29014272</v>
       </c>
       <c r="Q61">
-        <v>33.043570608</v>
+        <v>32.46114272</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1454225213659649</v>
+        <v>0.1475102714439006</v>
       </c>
       <c r="T61">
-        <v>1.298415418122545</v>
+        <v>1.325625800405685</v>
       </c>
       <c r="U61">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.32</v>
       </c>
       <c r="W61">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.551430429203253</v>
+        <v>4.28199309727839</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08258650857756022</v>
+        <v>0.08236042339507485</v>
       </c>
       <c r="C62">
-        <v>269.8604334901808</v>
+        <v>268.8025132417033</v>
       </c>
       <c r="D62">
-        <v>503.5804334901808</v>
+        <v>506.6945132417033</v>
       </c>
       <c r="E62">
-        <v>75.92000000000002</v>
+        <v>80.09200000000001</v>
       </c>
       <c r="F62">
-        <v>250.32</v>
+        <v>254.492</v>
       </c>
       <c r="G62">
         <v>16.6</v>
@@ -6371,28 +6371,28 @@
         <v>61.954</v>
       </c>
       <c r="M62">
-        <v>14.468496</v>
+        <v>14.7096376</v>
       </c>
       <c r="N62">
-        <v>47.485504</v>
+        <v>47.2443624</v>
       </c>
       <c r="O62">
-        <v>15.19536128</v>
+        <v>15.118195968</v>
       </c>
       <c r="P62">
-        <v>32.29014272</v>
+        <v>32.126166432</v>
       </c>
       <c r="Q62">
-        <v>32.46114272</v>
+        <v>32.297166432</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1475102714439006</v>
+        <v>0.149705085628397</v>
       </c>
       <c r="T62">
-        <v>1.325625800405685</v>
+        <v>1.354231586908474</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.28199309727839</v>
+        <v>4.211796489126285</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08236042339507485</v>
+        <v>0.08213433821258946</v>
       </c>
       <c r="C63">
-        <v>268.8025132417033</v>
+        <v>267.7833468180391</v>
       </c>
       <c r="D63">
-        <v>506.6945132417033</v>
+        <v>509.8473468180392</v>
       </c>
       <c r="E63">
-        <v>80.09200000000001</v>
+        <v>84.26400000000004</v>
       </c>
       <c r="F63">
-        <v>254.492</v>
+        <v>258.664</v>
       </c>
       <c r="G63">
         <v>16.6</v>
@@ -6453,28 +6453,28 @@
         <v>61.954</v>
       </c>
       <c r="M63">
-        <v>14.7096376</v>
+        <v>14.9507792</v>
       </c>
       <c r="N63">
-        <v>47.2443624</v>
+        <v>47.00322079999999</v>
       </c>
       <c r="O63">
-        <v>15.118195968</v>
+        <v>15.041030656</v>
       </c>
       <c r="P63">
-        <v>32.126166432</v>
+        <v>31.962190144</v>
       </c>
       <c r="Q63">
-        <v>32.297166432</v>
+        <v>32.133190144</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.149705085628397</v>
+        <v>0.1520154163489196</v>
       </c>
       <c r="T63">
-        <v>1.354231586908474</v>
+        <v>1.384342941121935</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.211796489126285</v>
+        <v>4.143864287688764</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08213433821258946</v>
+        <v>0.08190825303010407</v>
       </c>
       <c r="C64">
-        <v>267.7833468180391</v>
+        <v>266.8036621690185</v>
       </c>
       <c r="D64">
-        <v>509.8473468180392</v>
+        <v>513.0396621690185</v>
       </c>
       <c r="E64">
-        <v>84.26400000000004</v>
+        <v>88.43600000000001</v>
       </c>
       <c r="F64">
-        <v>258.664</v>
+        <v>262.836</v>
       </c>
       <c r="G64">
         <v>16.6</v>
@@ -6535,28 +6535,28 @@
         <v>61.954</v>
       </c>
       <c r="M64">
-        <v>14.9507792</v>
+        <v>15.1919208</v>
       </c>
       <c r="N64">
-        <v>47.00322079999999</v>
+        <v>46.7620792</v>
       </c>
       <c r="O64">
-        <v>15.041030656</v>
+        <v>14.963865344</v>
       </c>
       <c r="P64">
-        <v>31.962190144</v>
+        <v>31.798213856</v>
       </c>
       <c r="Q64">
-        <v>32.133190144</v>
+        <v>31.969213856</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1520154163489196</v>
+        <v>0.1544506298110921</v>
       </c>
       <c r="T64">
-        <v>1.384342941121935</v>
+        <v>1.416081936103692</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.143864287688764</v>
+        <v>4.078088664074658</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08190825303010407</v>
+        <v>0.08168216784761868</v>
       </c>
       <c r="C65">
-        <v>266.8036621690185</v>
+        <v>265.8642055910409</v>
       </c>
       <c r="D65">
-        <v>513.0396621690185</v>
+        <v>516.2722055910409</v>
       </c>
       <c r="E65">
-        <v>88.43600000000001</v>
+        <v>92.60800000000003</v>
       </c>
       <c r="F65">
-        <v>262.836</v>
+        <v>267.008</v>
       </c>
       <c r="G65">
         <v>16.6</v>
@@ -6617,28 +6617,28 @@
         <v>61.954</v>
       </c>
       <c r="M65">
-        <v>15.1919208</v>
+        <v>15.4330624</v>
       </c>
       <c r="N65">
-        <v>46.7620792</v>
+        <v>46.5209376</v>
       </c>
       <c r="O65">
-        <v>14.963865344</v>
+        <v>14.886700032</v>
       </c>
       <c r="P65">
-        <v>31.798213856</v>
+        <v>31.634237568</v>
       </c>
       <c r="Q65">
-        <v>31.969213856</v>
+        <v>31.805237568</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1544506298110921</v>
+        <v>0.1570211329100519</v>
       </c>
       <c r="T65">
-        <v>1.416081936103692</v>
+        <v>1.449584208584435</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.078088664074658</v>
+        <v>4.01436852869849</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08168216784761868</v>
+        <v>0.08300308266513329</v>
       </c>
       <c r="C66">
-        <v>265.8642055910409</v>
+        <v>243.3616921662682</v>
       </c>
       <c r="D66">
-        <v>516.2722055910409</v>
+        <v>497.9416921662683</v>
       </c>
       <c r="E66">
-        <v>92.60800000000003</v>
+        <v>96.78000000000006</v>
       </c>
       <c r="F66">
-        <v>267.008</v>
+        <v>271.1800000000001</v>
       </c>
       <c r="G66">
         <v>16.6</v>
@@ -6699,45 +6699,45 @@
         <v>61.954</v>
       </c>
       <c r="M66">
-        <v>15.4330624</v>
+        <v>16.623334</v>
       </c>
       <c r="N66">
-        <v>46.5209376</v>
+        <v>45.33066599999999</v>
       </c>
       <c r="O66">
-        <v>14.886700032</v>
+        <v>14.50581312</v>
       </c>
       <c r="P66">
-        <v>31.634237568</v>
+        <v>30.82485287999999</v>
       </c>
       <c r="Q66">
-        <v>31.805237568</v>
+        <v>30.99585287999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1570211329100519</v>
+        <v>0.1597385219003808</v>
       </c>
       <c r="T66">
-        <v>1.449584208584435</v>
+        <v>1.485000896635506</v>
       </c>
       <c r="U66">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V66">
         <v>0.32</v>
       </c>
       <c r="W66">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.01436852869849</v>
+        <v>3.726929868581115</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08300308266513329</v>
+        <v>0.08280079748264792</v>
       </c>
       <c r="C67">
-        <v>243.3616921662682</v>
+        <v>241.9119639257936</v>
       </c>
       <c r="D67">
-        <v>497.9416921662683</v>
+        <v>500.6639639257936</v>
       </c>
       <c r="E67">
-        <v>96.78000000000006</v>
+        <v>100.952</v>
       </c>
       <c r="F67">
-        <v>271.1800000000001</v>
+        <v>275.352</v>
       </c>
       <c r="G67">
         <v>16.6</v>
@@ -6781,28 +6781,28 @@
         <v>61.954</v>
       </c>
       <c r="M67">
-        <v>16.623334</v>
+        <v>16.8790776</v>
       </c>
       <c r="N67">
-        <v>45.33066599999999</v>
+        <v>45.0749224</v>
       </c>
       <c r="O67">
-        <v>14.50581312</v>
+        <v>14.423975168</v>
       </c>
       <c r="P67">
-        <v>30.82485287999999</v>
+        <v>30.650947232</v>
       </c>
       <c r="Q67">
-        <v>30.99585287999999</v>
+        <v>30.821947232</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1597385219003808</v>
+        <v>0.1626157573019056</v>
       </c>
       <c r="T67">
-        <v>1.485000896635506</v>
+        <v>1.522500919277817</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.726929868581115</v>
+        <v>3.670461234208675</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08280079748264792</v>
+        <v>0.08259851230016252</v>
       </c>
       <c r="C68">
-        <v>241.9119639257936</v>
+        <v>240.4921648974112</v>
       </c>
       <c r="D68">
-        <v>500.6639639257936</v>
+        <v>503.4161648974113</v>
       </c>
       <c r="E68">
-        <v>100.952</v>
+        <v>105.1240000000001</v>
       </c>
       <c r="F68">
-        <v>275.352</v>
+        <v>279.5240000000001</v>
       </c>
       <c r="G68">
         <v>16.6</v>
@@ -6863,28 +6863,28 @@
         <v>61.954</v>
       </c>
       <c r="M68">
-        <v>16.8790776</v>
+        <v>17.1348212</v>
       </c>
       <c r="N68">
-        <v>45.0749224</v>
+        <v>44.8191788</v>
       </c>
       <c r="O68">
-        <v>14.423975168</v>
+        <v>14.342137216</v>
       </c>
       <c r="P68">
-        <v>30.650947232</v>
+        <v>30.477041584</v>
       </c>
       <c r="Q68">
-        <v>30.821947232</v>
+        <v>30.648041584</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1626157573019056</v>
+        <v>0.1656673706065531</v>
       </c>
       <c r="T68">
-        <v>1.522500919277817</v>
+        <v>1.562273670565116</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.670461234208675</v>
+        <v>3.615678230713022</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08259851230016252</v>
+        <v>0.08239622711767713</v>
       </c>
       <c r="C69">
-        <v>240.4921648974112</v>
+        <v>239.1027913811446</v>
       </c>
       <c r="D69">
-        <v>503.4161648974113</v>
+        <v>506.1987913811446</v>
       </c>
       <c r="E69">
-        <v>105.1240000000001</v>
+        <v>109.296</v>
       </c>
       <c r="F69">
-        <v>279.5240000000001</v>
+        <v>283.696</v>
       </c>
       <c r="G69">
         <v>16.6</v>
@@ -6945,28 +6945,28 @@
         <v>61.954</v>
       </c>
       <c r="M69">
-        <v>17.1348212</v>
+        <v>17.3905648</v>
       </c>
       <c r="N69">
-        <v>44.8191788</v>
+        <v>44.5634352</v>
       </c>
       <c r="O69">
-        <v>14.342137216</v>
+        <v>14.260299264</v>
       </c>
       <c r="P69">
-        <v>30.477041584</v>
+        <v>30.303135936</v>
       </c>
       <c r="Q69">
-        <v>30.648041584</v>
+        <v>30.474135936</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1656673706065531</v>
+        <v>0.1689097097427411</v>
       </c>
       <c r="T69">
-        <v>1.562273670565116</v>
+        <v>1.604532218807872</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.615678230713022</v>
+        <v>3.562506492026067</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08239622711767713</v>
+        <v>0.08219394193519175</v>
       </c>
       <c r="C70">
-        <v>239.1027913811446</v>
+        <v>237.7443507111768</v>
       </c>
       <c r="D70">
-        <v>506.1987913811446</v>
+        <v>509.0123507111769</v>
       </c>
       <c r="E70">
-        <v>109.296</v>
+        <v>113.468</v>
       </c>
       <c r="F70">
-        <v>283.696</v>
+        <v>287.8680000000001</v>
       </c>
       <c r="G70">
         <v>16.6</v>
@@ -7027,28 +7027,28 @@
         <v>61.954</v>
       </c>
       <c r="M70">
-        <v>17.3905648</v>
+        <v>17.6463084</v>
       </c>
       <c r="N70">
-        <v>44.5634352</v>
+        <v>44.3076916</v>
       </c>
       <c r="O70">
-        <v>14.260299264</v>
+        <v>14.178461312</v>
       </c>
       <c r="P70">
-        <v>30.303135936</v>
+        <v>30.129230288</v>
       </c>
       <c r="Q70">
-        <v>30.474135936</v>
+        <v>30.300230288</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1689097097427411</v>
+        <v>0.1723612320490057</v>
       </c>
       <c r="T70">
-        <v>1.604532218807872</v>
+        <v>1.649517125001773</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.562506492026067</v>
+        <v>3.510875963156123</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08219394193519175</v>
+        <v>0.08332445675270636</v>
       </c>
       <c r="C71">
-        <v>237.7443507111768</v>
+        <v>218.2371252455762</v>
       </c>
       <c r="D71">
-        <v>509.0123507111769</v>
+        <v>493.6771252455763</v>
       </c>
       <c r="E71">
-        <v>113.468</v>
+        <v>117.6400000000001</v>
       </c>
       <c r="F71">
-        <v>287.8680000000001</v>
+        <v>292.0400000000001</v>
       </c>
       <c r="G71">
         <v>16.6</v>
@@ -7109,45 +7109,45 @@
         <v>61.954</v>
       </c>
       <c r="M71">
-        <v>17.6463084</v>
+        <v>18.719764</v>
       </c>
       <c r="N71">
-        <v>44.3076916</v>
+        <v>43.234236</v>
       </c>
       <c r="O71">
-        <v>14.178461312</v>
+        <v>13.83495552</v>
       </c>
       <c r="P71">
-        <v>30.129230288</v>
+        <v>29.39928047999999</v>
       </c>
       <c r="Q71">
-        <v>30.300230288</v>
+        <v>29.57028047999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1723612320490057</v>
+        <v>0.1760428558423546</v>
       </c>
       <c r="T71">
-        <v>1.649517125001773</v>
+        <v>1.697501024941934</v>
       </c>
       <c r="U71">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V71">
         <v>0.32</v>
       </c>
       <c r="W71">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.510875963156123</v>
+        <v>3.309550269971351</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08332445675270636</v>
+        <v>0.08314121157022097</v>
       </c>
       <c r="C72">
-        <v>218.2371252455762</v>
+        <v>216.4877556611526</v>
       </c>
       <c r="D72">
-        <v>493.6771252455763</v>
+        <v>496.0997556611526</v>
       </c>
       <c r="E72">
-        <v>117.6400000000001</v>
+        <v>121.812</v>
       </c>
       <c r="F72">
-        <v>292.0400000000001</v>
+        <v>296.212</v>
       </c>
       <c r="G72">
         <v>16.6</v>
@@ -7191,28 +7191,28 @@
         <v>61.954</v>
       </c>
       <c r="M72">
-        <v>18.719764</v>
+        <v>18.9871892</v>
       </c>
       <c r="N72">
-        <v>43.234236</v>
+        <v>42.9668108</v>
       </c>
       <c r="O72">
-        <v>13.83495552</v>
+        <v>13.749379456</v>
       </c>
       <c r="P72">
-        <v>29.39928047999999</v>
+        <v>29.217431344</v>
       </c>
       <c r="Q72">
-        <v>29.57028047999999</v>
+        <v>29.388431344</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1760428558423546</v>
+        <v>0.1799783847249</v>
       </c>
       <c r="T72">
-        <v>1.697501024941934</v>
+        <v>1.748794159360727</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.309550269971351</v>
+        <v>3.262936885887248</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08314121157022097</v>
+        <v>0.08295796638773559</v>
       </c>
       <c r="C73">
-        <v>216.4877556611526</v>
+        <v>214.7622805680455</v>
       </c>
       <c r="D73">
-        <v>496.0997556611526</v>
+        <v>498.5462805680455</v>
       </c>
       <c r="E73">
-        <v>121.812</v>
+        <v>125.984</v>
       </c>
       <c r="F73">
-        <v>296.212</v>
+        <v>300.384</v>
       </c>
       <c r="G73">
         <v>16.6</v>
@@ -7273,28 +7273,28 @@
         <v>61.954</v>
       </c>
       <c r="M73">
-        <v>18.9871892</v>
+        <v>19.2546144</v>
       </c>
       <c r="N73">
-        <v>42.9668108</v>
+        <v>42.6993856</v>
       </c>
       <c r="O73">
-        <v>13.749379456</v>
+        <v>13.663803392</v>
       </c>
       <c r="P73">
-        <v>29.217431344</v>
+        <v>29.035582208</v>
       </c>
       <c r="Q73">
-        <v>29.388431344</v>
+        <v>29.206582208</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1799783847248999</v>
+        <v>0.1841950228133414</v>
       </c>
       <c r="T73">
-        <v>1.748794159360726</v>
+        <v>1.803751089095147</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.262936885887249</v>
+        <v>3.217618318027703</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08295796638773559</v>
+        <v>0.0827747212052502</v>
       </c>
       <c r="C74">
-        <v>214.7622805680455</v>
+        <v>213.0610552265744</v>
       </c>
       <c r="D74">
-        <v>498.5462805680455</v>
+        <v>501.0170552265744</v>
       </c>
       <c r="E74">
-        <v>125.984</v>
+        <v>130.156</v>
       </c>
       <c r="F74">
-        <v>300.384</v>
+        <v>304.556</v>
       </c>
       <c r="G74">
         <v>16.6</v>
@@ -7355,28 +7355,28 @@
         <v>61.954</v>
       </c>
       <c r="M74">
-        <v>19.2546144</v>
+        <v>19.5220396</v>
       </c>
       <c r="N74">
-        <v>42.6993856</v>
+        <v>42.43196039999999</v>
       </c>
       <c r="O74">
-        <v>13.663803392</v>
+        <v>13.578227328</v>
       </c>
       <c r="P74">
-        <v>29.035582208</v>
+        <v>28.853733072</v>
       </c>
       <c r="Q74">
-        <v>29.206582208</v>
+        <v>29.024733072</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1841950228133414</v>
+        <v>0.1887240044638896</v>
       </c>
       <c r="T74">
-        <v>1.803751089095147</v>
+        <v>1.862778902513599</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.217618318027703</v>
+        <v>3.173541354767049</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0827747212052502</v>
+        <v>0.08259147602276481</v>
       </c>
       <c r="C75">
-        <v>213.0610552265744</v>
+        <v>211.384441974757</v>
       </c>
       <c r="D75">
-        <v>501.0170552265744</v>
+        <v>503.5124419747569</v>
       </c>
       <c r="E75">
-        <v>130.156</v>
+        <v>134.328</v>
       </c>
       <c r="F75">
-        <v>304.556</v>
+        <v>308.728</v>
       </c>
       <c r="G75">
         <v>16.6</v>
@@ -7437,28 +7437,28 @@
         <v>61.954</v>
       </c>
       <c r="M75">
-        <v>19.5220396</v>
+        <v>19.7894648</v>
       </c>
       <c r="N75">
-        <v>42.43196039999999</v>
+        <v>42.1645352</v>
       </c>
       <c r="O75">
-        <v>13.578227328</v>
+        <v>13.492651264</v>
       </c>
       <c r="P75">
-        <v>28.853733072</v>
+        <v>28.671883936</v>
       </c>
       <c r="Q75">
-        <v>29.024733072</v>
+        <v>28.842883936</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1887240044638896</v>
+        <v>0.1936013693183262</v>
       </c>
       <c r="T75">
-        <v>1.862778902513599</v>
+        <v>1.92634731696424</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.173541354767049</v>
+        <v>3.130655660783712</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08259147602276481</v>
+        <v>0.08240823084027943</v>
       </c>
       <c r="C76">
-        <v>211.384441974757</v>
+        <v>209.732810405449</v>
       </c>
       <c r="D76">
-        <v>503.5124419747569</v>
+        <v>506.032810405449</v>
       </c>
       <c r="E76">
-        <v>134.328</v>
+        <v>138.5</v>
       </c>
       <c r="F76">
-        <v>308.728</v>
+        <v>312.9</v>
       </c>
       <c r="G76">
         <v>16.6</v>
@@ -7519,28 +7519,28 @@
         <v>61.954</v>
       </c>
       <c r="M76">
-        <v>19.7894648</v>
+        <v>20.05689</v>
       </c>
       <c r="N76">
-        <v>42.1645352</v>
+        <v>41.89711</v>
       </c>
       <c r="O76">
-        <v>13.492651264</v>
+        <v>13.4070752</v>
       </c>
       <c r="P76">
-        <v>28.671883936</v>
+        <v>28.4900348</v>
       </c>
       <c r="Q76">
-        <v>28.842883936</v>
+        <v>28.6610348</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1936013693183262</v>
+        <v>0.1988689233611177</v>
       </c>
       <c r="T76">
-        <v>1.92634731696424</v>
+        <v>1.995001204570932</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.130655660783712</v>
+        <v>3.088913585306595</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08240823084027943</v>
+        <v>0.08222498565779404</v>
       </c>
       <c r="C77">
-        <v>209.732810405449</v>
+        <v>208.1065375488308</v>
       </c>
       <c r="D77">
-        <v>506.032810405449</v>
+        <v>508.5785375488309</v>
       </c>
       <c r="E77">
-        <v>138.5</v>
+        <v>142.6720000000001</v>
       </c>
       <c r="F77">
-        <v>312.9</v>
+        <v>317.0720000000001</v>
       </c>
       <c r="G77">
         <v>16.6</v>
@@ -7601,28 +7601,28 @@
         <v>61.954</v>
       </c>
       <c r="M77">
-        <v>20.05689</v>
+        <v>20.3243152</v>
       </c>
       <c r="N77">
-        <v>41.89711</v>
+        <v>41.62968479999999</v>
       </c>
       <c r="O77">
-        <v>13.4070752</v>
+        <v>13.321499136</v>
       </c>
       <c r="P77">
-        <v>28.4900348</v>
+        <v>28.30818566399999</v>
       </c>
       <c r="Q77">
-        <v>28.6610348</v>
+        <v>28.47918566399999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1988689233611177</v>
+        <v>0.2045754402408085</v>
       </c>
       <c r="T77">
-        <v>1.995001204570932</v>
+        <v>2.069376249478182</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.088913585306595</v>
+        <v>3.048269985499929</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08222498565779404</v>
+        <v>0.08204174047530866</v>
       </c>
       <c r="C78">
-        <v>208.1065375488308</v>
+        <v>206.50600806043</v>
       </c>
       <c r="D78">
-        <v>508.5785375488309</v>
+        <v>511.15000806043</v>
       </c>
       <c r="E78">
-        <v>142.6720000000001</v>
+        <v>146.844</v>
       </c>
       <c r="F78">
-        <v>317.0720000000001</v>
+        <v>321.244</v>
       </c>
       <c r="G78">
         <v>16.6</v>
@@ -7683,28 +7683,28 @@
         <v>61.954</v>
       </c>
       <c r="M78">
-        <v>20.3243152</v>
+        <v>20.5917404</v>
       </c>
       <c r="N78">
-        <v>41.62968479999999</v>
+        <v>41.3622596</v>
       </c>
       <c r="O78">
-        <v>13.321499136</v>
+        <v>13.235923072</v>
       </c>
       <c r="P78">
-        <v>28.30818566399999</v>
+        <v>28.126336528</v>
       </c>
       <c r="Q78">
-        <v>28.47918566399999</v>
+        <v>28.297336528</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2045754402408085</v>
+        <v>0.2107781759796028</v>
       </c>
       <c r="T78">
-        <v>2.069376249478182</v>
+        <v>2.150218689594757</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.048269985499929</v>
+        <v>3.00868206361032</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08204174047530866</v>
+        <v>0.08599561529282326</v>
       </c>
       <c r="C79">
-        <v>206.50600806043</v>
+        <v>152.0543163547686</v>
       </c>
       <c r="D79">
-        <v>511.15000806043</v>
+        <v>460.8703163547686</v>
       </c>
       <c r="E79">
-        <v>146.844</v>
+        <v>151.016</v>
       </c>
       <c r="F79">
-        <v>321.244</v>
+        <v>325.4160000000001</v>
       </c>
       <c r="G79">
         <v>16.6</v>
@@ -7765,45 +7765,45 @@
         <v>61.954</v>
       </c>
       <c r="M79">
-        <v>20.5917404</v>
+        <v>23.39741040000001</v>
       </c>
       <c r="N79">
-        <v>41.3622596</v>
+        <v>38.5565896</v>
       </c>
       <c r="O79">
-        <v>13.235923072</v>
+        <v>12.338108672</v>
       </c>
       <c r="P79">
-        <v>28.126336528</v>
+        <v>26.218480928</v>
       </c>
       <c r="Q79">
-        <v>28.297336528</v>
+        <v>26.389480928</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2107781759796028</v>
+        <v>0.2175447967855603</v>
       </c>
       <c r="T79">
-        <v>2.150218689594757</v>
+        <v>2.238410442449204</v>
       </c>
       <c r="U79">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V79">
         <v>0.32</v>
       </c>
       <c r="W79">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.00868206361032</v>
+        <v>2.647899871859323</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08599561529282326</v>
+        <v>0.08586541011033788</v>
       </c>
       <c r="C80">
-        <v>152.0543163547686</v>
+        <v>149.3800597568156</v>
       </c>
       <c r="D80">
-        <v>460.8703163547686</v>
+        <v>462.3680597568156</v>
       </c>
       <c r="E80">
-        <v>151.016</v>
+        <v>155.1880000000001</v>
       </c>
       <c r="F80">
-        <v>325.4160000000001</v>
+        <v>329.5880000000001</v>
       </c>
       <c r="G80">
         <v>16.6</v>
@@ -7847,28 +7847,28 @@
         <v>61.954</v>
       </c>
       <c r="M80">
-        <v>23.39741040000001</v>
+        <v>23.69737720000001</v>
       </c>
       <c r="N80">
-        <v>38.5565896</v>
+        <v>38.25662279999999</v>
       </c>
       <c r="O80">
-        <v>12.338108672</v>
+        <v>12.242119296</v>
       </c>
       <c r="P80">
-        <v>26.218480928</v>
+        <v>26.01450350399999</v>
       </c>
       <c r="Q80">
-        <v>26.389480928</v>
+        <v>26.18550350399999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2175447967855603</v>
+        <v>0.2249558576682756</v>
       </c>
       <c r="T80">
-        <v>2.238410442449204</v>
+        <v>2.335001409861217</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.647899871859323</v>
+        <v>2.614382151962369</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08586541011033788</v>
+        <v>0.08573520492785248</v>
       </c>
       <c r="C81">
-        <v>149.3800597568156</v>
+        <v>146.7155696770682</v>
       </c>
       <c r="D81">
-        <v>462.3680597568156</v>
+        <v>463.8755696770682</v>
       </c>
       <c r="E81">
-        <v>155.1880000000001</v>
+        <v>159.36</v>
       </c>
       <c r="F81">
-        <v>329.5880000000001</v>
+        <v>333.76</v>
       </c>
       <c r="G81">
         <v>16.6</v>
@@ -7929,28 +7929,28 @@
         <v>61.954</v>
       </c>
       <c r="M81">
-        <v>23.69737720000001</v>
+        <v>23.99734400000001</v>
       </c>
       <c r="N81">
-        <v>38.25662279999999</v>
+        <v>37.956656</v>
       </c>
       <c r="O81">
-        <v>12.242119296</v>
+        <v>12.14612992</v>
       </c>
       <c r="P81">
-        <v>26.01450350399999</v>
+        <v>25.81052608</v>
       </c>
       <c r="Q81">
-        <v>26.18550350399999</v>
+        <v>25.98152607999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2249558576682756</v>
+        <v>0.2331080246392625</v>
       </c>
       <c r="T81">
-        <v>2.335001409861217</v>
+        <v>2.44125147401443</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.614382151962369</v>
+        <v>2.58170237506284</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08573520492785248</v>
+        <v>0.08560499974536709</v>
       </c>
       <c r="C82">
-        <v>146.7155696770682</v>
+        <v>144.0609419565982</v>
       </c>
       <c r="D82">
-        <v>463.8755696770682</v>
+        <v>465.3929419565982</v>
       </c>
       <c r="E82">
-        <v>159.36</v>
+        <v>163.5320000000001</v>
       </c>
       <c r="F82">
-        <v>333.76</v>
+        <v>337.9320000000001</v>
       </c>
       <c r="G82">
         <v>16.6</v>
@@ -8011,28 +8011,28 @@
         <v>61.954</v>
       </c>
       <c r="M82">
-        <v>23.99734400000001</v>
+        <v>24.29731080000001</v>
       </c>
       <c r="N82">
-        <v>37.956656</v>
+        <v>37.65668919999999</v>
       </c>
       <c r="O82">
-        <v>12.14612992</v>
+        <v>12.050140544</v>
       </c>
       <c r="P82">
-        <v>25.81052608</v>
+        <v>25.60654865599999</v>
       </c>
       <c r="Q82">
-        <v>25.98152607999999</v>
+        <v>25.77754865599999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2331080246392625</v>
+        <v>0.2421183144493006</v>
       </c>
       <c r="T82">
-        <v>2.44125147401443</v>
+        <v>2.55868575544693</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.58170237506284</v>
+        <v>2.549829506234903</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08560499974536709</v>
+        <v>0.08547479456288171</v>
       </c>
       <c r="C83">
-        <v>144.0609419565982</v>
+        <v>141.416273694607</v>
       </c>
       <c r="D83">
-        <v>465.3929419565982</v>
+        <v>466.920273694607</v>
       </c>
       <c r="E83">
-        <v>163.5320000000001</v>
+        <v>167.704</v>
       </c>
       <c r="F83">
-        <v>337.9320000000001</v>
+        <v>342.104</v>
       </c>
       <c r="G83">
         <v>16.6</v>
@@ -8093,28 +8093,28 @@
         <v>61.954</v>
       </c>
       <c r="M83">
-        <v>24.29731080000001</v>
+        <v>24.59727760000001</v>
       </c>
       <c r="N83">
-        <v>37.65668919999999</v>
+        <v>37.3567224</v>
       </c>
       <c r="O83">
-        <v>12.050140544</v>
+        <v>11.954151168</v>
       </c>
       <c r="P83">
-        <v>25.60654865599999</v>
+        <v>25.402571232</v>
       </c>
       <c r="Q83">
-        <v>25.77754865599999</v>
+        <v>25.573571232</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2421183144493006</v>
+        <v>0.2521297475715651</v>
       </c>
       <c r="T83">
-        <v>2.55868575544693</v>
+        <v>2.68916829037193</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.549829506234903</v>
+        <v>2.518734024451551</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08547479456288171</v>
+        <v>0.08754574938039632</v>
       </c>
       <c r="C84">
-        <v>141.416273694607</v>
+        <v>114.0809383956802</v>
       </c>
       <c r="D84">
-        <v>466.920273694607</v>
+        <v>443.7569383956802</v>
       </c>
       <c r="E84">
-        <v>167.704</v>
+        <v>171.8760000000001</v>
       </c>
       <c r="F84">
-        <v>342.104</v>
+        <v>346.2760000000001</v>
       </c>
       <c r="G84">
         <v>16.6</v>
@@ -8175,45 +8175,45 @@
         <v>61.954</v>
       </c>
       <c r="M84">
-        <v>24.59727760000001</v>
+        <v>26.24772080000001</v>
       </c>
       <c r="N84">
-        <v>37.3567224</v>
+        <v>35.7062792</v>
       </c>
       <c r="O84">
-        <v>11.954151168</v>
+        <v>11.426009344</v>
       </c>
       <c r="P84">
-        <v>25.402571232</v>
+        <v>24.280269856</v>
       </c>
       <c r="Q84">
-        <v>25.573571232</v>
+        <v>24.451269856</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2521297475715651</v>
+        <v>0.2633189963552726</v>
       </c>
       <c r="T84">
-        <v>2.68916829037193</v>
+        <v>2.835001711758694</v>
       </c>
       <c r="U84">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.32</v>
       </c>
       <c r="W84">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.518734024451551</v>
+        <v>2.360357322910871</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08754574938039632</v>
+        <v>0.08744206419791094</v>
       </c>
       <c r="C85">
-        <v>114.0809383956802</v>
+        <v>111.0138552633462</v>
       </c>
       <c r="D85">
-        <v>443.7569383956802</v>
+        <v>444.8618552633463</v>
       </c>
       <c r="E85">
-        <v>171.8760000000001</v>
+        <v>176.0480000000001</v>
       </c>
       <c r="F85">
-        <v>346.2760000000001</v>
+        <v>350.4480000000001</v>
       </c>
       <c r="G85">
         <v>16.6</v>
@@ -8257,28 +8257,28 @@
         <v>61.954</v>
       </c>
       <c r="M85">
-        <v>26.24772080000001</v>
+        <v>26.56395840000001</v>
       </c>
       <c r="N85">
-        <v>35.7062792</v>
+        <v>35.39004159999999</v>
       </c>
       <c r="O85">
-        <v>11.426009344</v>
+        <v>11.324813312</v>
       </c>
       <c r="P85">
-        <v>24.280269856</v>
+        <v>24.06522828799999</v>
       </c>
       <c r="Q85">
-        <v>24.451269856</v>
+        <v>24.23622828799999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2633189963552726</v>
+        <v>0.2759069012369435</v>
       </c>
       <c r="T85">
-        <v>2.835001711758694</v>
+        <v>2.999064310818804</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.360357322910871</v>
+        <v>2.332257830971455</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08744206419791094</v>
+        <v>0.08733837901542557</v>
       </c>
       <c r="C86">
-        <v>111.0138552633463</v>
+        <v>107.9522881626809</v>
       </c>
       <c r="D86">
-        <v>444.8618552633463</v>
+        <v>445.9722881626809</v>
       </c>
       <c r="E86">
-        <v>176.048</v>
+        <v>180.22</v>
       </c>
       <c r="F86">
-        <v>350.448</v>
+        <v>354.62</v>
       </c>
       <c r="G86">
         <v>16.6</v>
@@ -8339,28 +8339,28 @@
         <v>61.954</v>
       </c>
       <c r="M86">
-        <v>26.5639584</v>
+        <v>26.880196</v>
       </c>
       <c r="N86">
-        <v>35.3900416</v>
+        <v>35.073804</v>
       </c>
       <c r="O86">
-        <v>11.324813312</v>
+        <v>11.22361728</v>
       </c>
       <c r="P86">
-        <v>24.065228288</v>
+        <v>23.85018672</v>
       </c>
       <c r="Q86">
-        <v>24.236228288</v>
+        <v>24.02118672</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2759069012369433</v>
+        <v>0.2901731934361704</v>
       </c>
       <c r="T86">
-        <v>2.999064310818802</v>
+        <v>3.185001923086927</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.332257830971456</v>
+        <v>2.304819503548263</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08733837901542557</v>
+        <v>0.08723469383294016</v>
       </c>
       <c r="C87">
-        <v>107.9522881626809</v>
+        <v>104.89627850324</v>
       </c>
       <c r="D87">
-        <v>445.9722881626809</v>
+        <v>447.08827850324</v>
       </c>
       <c r="E87">
-        <v>180.22</v>
+        <v>184.392</v>
       </c>
       <c r="F87">
-        <v>354.62</v>
+        <v>358.792</v>
       </c>
       <c r="G87">
         <v>16.6</v>
@@ -8421,28 +8421,28 @@
         <v>61.954</v>
       </c>
       <c r="M87">
-        <v>26.880196</v>
+        <v>27.19643360000001</v>
       </c>
       <c r="N87">
-        <v>35.073804</v>
+        <v>34.75756639999999</v>
       </c>
       <c r="O87">
-        <v>11.22361728</v>
+        <v>11.122421248</v>
       </c>
       <c r="P87">
-        <v>23.85018672</v>
+        <v>23.635145152</v>
       </c>
       <c r="Q87">
-        <v>24.02118672</v>
+        <v>23.806145152</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2901731934361704</v>
+        <v>0.306477527378144</v>
       </c>
       <c r="T87">
-        <v>3.185001923086927</v>
+        <v>3.397502051393354</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.304819503548263</v>
+        <v>2.278019276762818</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08723469383294016</v>
+        <v>0.08713100865045478</v>
       </c>
       <c r="C88">
-        <v>104.89627850324</v>
+        <v>101.8458681101071</v>
       </c>
       <c r="D88">
-        <v>447.08827850324</v>
+        <v>448.2098681101071</v>
       </c>
       <c r="E88">
-        <v>184.392</v>
+        <v>188.564</v>
       </c>
       <c r="F88">
-        <v>358.792</v>
+        <v>362.9640000000001</v>
       </c>
       <c r="G88">
         <v>16.6</v>
@@ -8503,28 +8503,28 @@
         <v>61.954</v>
       </c>
       <c r="M88">
-        <v>27.19643360000001</v>
+        <v>27.51267120000001</v>
       </c>
       <c r="N88">
-        <v>34.75756639999999</v>
+        <v>34.44132879999999</v>
       </c>
       <c r="O88">
-        <v>11.122421248</v>
+        <v>11.021225216</v>
       </c>
       <c r="P88">
-        <v>23.635145152</v>
+        <v>23.420103584</v>
       </c>
       <c r="Q88">
-        <v>23.806145152</v>
+        <v>23.591103584</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.306477527378144</v>
+        <v>0.3252902203881137</v>
       </c>
       <c r="T88">
-        <v>3.397502051393354</v>
+        <v>3.64269450713154</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.278019276762818</v>
+        <v>2.251835147144854</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08713100865045478</v>
+        <v>0.0870273234679694</v>
       </c>
       <c r="C89">
-        <v>101.8458681101071</v>
+        <v>98.80109922912084</v>
       </c>
       <c r="D89">
-        <v>448.2098681101071</v>
+        <v>449.3370992291208</v>
       </c>
       <c r="E89">
-        <v>188.564</v>
+        <v>192.736</v>
       </c>
       <c r="F89">
-        <v>362.9640000000001</v>
+        <v>367.136</v>
       </c>
       <c r="G89">
         <v>16.6</v>
@@ -8585,28 +8585,28 @@
         <v>61.954</v>
       </c>
       <c r="M89">
-        <v>27.51267120000001</v>
+        <v>27.8289088</v>
       </c>
       <c r="N89">
-        <v>34.44132879999999</v>
+        <v>34.1250912</v>
       </c>
       <c r="O89">
-        <v>11.021225216</v>
+        <v>10.920029184</v>
       </c>
       <c r="P89">
-        <v>23.420103584</v>
+        <v>23.205062016</v>
       </c>
       <c r="Q89">
-        <v>23.591103584</v>
+        <v>23.376062016</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3252902203881137</v>
+        <v>0.3472383622330783</v>
       </c>
       <c r="T89">
-        <v>3.64269450713154</v>
+        <v>3.928752372159424</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.251835147144854</v>
+        <v>2.226246111381845</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0870273234679694</v>
+        <v>0.086923638285484</v>
       </c>
       <c r="C90">
-        <v>98.80109922912084</v>
+        <v>95.76201453217857</v>
       </c>
       <c r="D90">
-        <v>449.3370992291208</v>
+        <v>450.4700145321786</v>
       </c>
       <c r="E90">
-        <v>192.736</v>
+        <v>196.908</v>
       </c>
       <c r="F90">
-        <v>367.136</v>
+        <v>371.308</v>
       </c>
       <c r="G90">
         <v>16.6</v>
@@ -8667,28 +8667,28 @@
         <v>61.954</v>
       </c>
       <c r="M90">
-        <v>27.8289088</v>
+        <v>28.14514640000001</v>
       </c>
       <c r="N90">
-        <v>34.1250912</v>
+        <v>33.80885359999999</v>
       </c>
       <c r="O90">
-        <v>10.920029184</v>
+        <v>10.818833152</v>
       </c>
       <c r="P90">
-        <v>23.205062016</v>
+        <v>22.990020448</v>
       </c>
       <c r="Q90">
-        <v>23.376062016</v>
+        <v>23.161020448</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3472383622330783</v>
+        <v>0.3731770753225819</v>
       </c>
       <c r="T90">
-        <v>3.928752372159424</v>
+        <v>4.266820758101468</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.226246111381845</v>
+        <v>2.201232110130363</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.086923638285484</v>
+        <v>0.08681995310299861</v>
       </c>
       <c r="C91">
-        <v>95.76201453217857</v>
+        <v>92.72865712261938</v>
       </c>
       <c r="D91">
-        <v>450.4700145321786</v>
+        <v>451.6086571226194</v>
       </c>
       <c r="E91">
-        <v>196.908</v>
+        <v>201.0800000000001</v>
       </c>
       <c r="F91">
-        <v>371.308</v>
+        <v>375.4800000000001</v>
       </c>
       <c r="G91">
         <v>16.6</v>
@@ -8749,28 +8749,28 @@
         <v>61.954</v>
       </c>
       <c r="M91">
-        <v>28.14514640000001</v>
+        <v>28.46138400000001</v>
       </c>
       <c r="N91">
-        <v>33.80885359999999</v>
+        <v>33.49261599999999</v>
       </c>
       <c r="O91">
-        <v>10.818833152</v>
+        <v>10.71763712</v>
       </c>
       <c r="P91">
-        <v>22.990020448</v>
+        <v>22.77497887999999</v>
       </c>
       <c r="Q91">
-        <v>23.161020448</v>
+        <v>22.94597887999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3731770753225819</v>
+        <v>0.4043035310299863</v>
       </c>
       <c r="T91">
-        <v>4.266820758101468</v>
+        <v>4.672502821231921</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.201232110130363</v>
+        <v>2.176773975573359</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08681995310299861</v>
+        <v>0.08671626792051323</v>
       </c>
       <c r="C92">
-        <v>92.72865712261938</v>
+        <v>89.70107054069314</v>
       </c>
       <c r="D92">
-        <v>451.6086571226194</v>
+        <v>452.7530705406932</v>
       </c>
       <c r="E92">
-        <v>201.0800000000001</v>
+        <v>205.252</v>
       </c>
       <c r="F92">
-        <v>375.4800000000001</v>
+        <v>379.652</v>
       </c>
       <c r="G92">
         <v>16.6</v>
@@ -8831,28 +8831,28 @@
         <v>61.954</v>
       </c>
       <c r="M92">
-        <v>28.46138400000001</v>
+        <v>28.77762160000001</v>
       </c>
       <c r="N92">
-        <v>33.49261599999999</v>
+        <v>33.17637839999999</v>
       </c>
       <c r="O92">
-        <v>10.71763712</v>
+        <v>10.616441088</v>
       </c>
       <c r="P92">
-        <v>22.77497887999999</v>
+        <v>22.559937312</v>
       </c>
       <c r="Q92">
-        <v>22.94597887999999</v>
+        <v>22.73093731199999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4043035310299863</v>
+        <v>0.4423469768945916</v>
       </c>
       <c r="T92">
-        <v>4.672502821231921</v>
+        <v>5.168336453946919</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.176773975573359</v>
+        <v>2.15285338243519</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08671626792051323</v>
+        <v>0.08661258273802785</v>
       </c>
       <c r="C93">
-        <v>89.70107054069314</v>
+        <v>86.67929876910881</v>
       </c>
       <c r="D93">
-        <v>452.7530705406932</v>
+        <v>453.9032987691089</v>
       </c>
       <c r="E93">
-        <v>205.252</v>
+        <v>209.4240000000001</v>
       </c>
       <c r="F93">
-        <v>379.652</v>
+        <v>383.8240000000001</v>
       </c>
       <c r="G93">
         <v>16.6</v>
@@ -8913,28 +8913,28 @@
         <v>61.954</v>
       </c>
       <c r="M93">
-        <v>28.77762160000001</v>
+        <v>29.09385920000001</v>
       </c>
       <c r="N93">
-        <v>33.17637839999999</v>
+        <v>32.8601408</v>
       </c>
       <c r="O93">
-        <v>10.616441088</v>
+        <v>10.515245056</v>
       </c>
       <c r="P93">
-        <v>22.559937312</v>
+        <v>22.344895744</v>
       </c>
       <c r="Q93">
-        <v>22.73093731199999</v>
+        <v>22.515895744</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4423469768945916</v>
+        <v>0.4899012842253483</v>
       </c>
       <c r="T93">
-        <v>5.168336453946919</v>
+        <v>5.788128494840667</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.15285338243519</v>
+        <v>2.129452802191329</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08661258273802785</v>
+        <v>0.08650889755554245</v>
       </c>
       <c r="C94">
-        <v>86.67929876910881</v>
+        <v>83.66338623866983</v>
       </c>
       <c r="D94">
-        <v>453.9032987691089</v>
+        <v>455.0593862386698</v>
       </c>
       <c r="E94">
-        <v>209.4240000000001</v>
+        <v>213.596</v>
       </c>
       <c r="F94">
-        <v>383.8240000000001</v>
+        <v>387.996</v>
       </c>
       <c r="G94">
         <v>16.6</v>
@@ -8995,28 +8995,28 @@
         <v>61.954</v>
       </c>
       <c r="M94">
-        <v>29.09385920000001</v>
+        <v>29.41009680000001</v>
       </c>
       <c r="N94">
-        <v>32.8601408</v>
+        <v>32.5439032</v>
       </c>
       <c r="O94">
-        <v>10.515245056</v>
+        <v>10.414049024</v>
       </c>
       <c r="P94">
-        <v>22.344895744</v>
+        <v>22.12985417599999</v>
       </c>
       <c r="Q94">
-        <v>22.515895744</v>
+        <v>22.30085417599999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4899012842253483</v>
+        <v>0.5510425365077496</v>
       </c>
       <c r="T94">
-        <v>5.788128494840667</v>
+        <v>6.585003975989772</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.129452802191329</v>
+        <v>2.106555460232283</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08650889755554245</v>
+        <v>0.08640521237305707</v>
       </c>
       <c r="C95">
-        <v>83.66338623866983</v>
+        <v>80.65337783399383</v>
       </c>
       <c r="D95">
-        <v>455.0593862386698</v>
+        <v>456.2213778339939</v>
       </c>
       <c r="E95">
-        <v>213.596</v>
+        <v>217.7680000000001</v>
       </c>
       <c r="F95">
-        <v>387.996</v>
+        <v>392.1680000000001</v>
       </c>
       <c r="G95">
         <v>16.6</v>
@@ -9077,28 +9077,28 @@
         <v>61.954</v>
       </c>
       <c r="M95">
-        <v>29.41009680000001</v>
+        <v>29.72633440000001</v>
       </c>
       <c r="N95">
-        <v>32.5439032</v>
+        <v>32.22766559999999</v>
       </c>
       <c r="O95">
-        <v>10.414049024</v>
+        <v>10.312852992</v>
       </c>
       <c r="P95">
-        <v>22.12985417599999</v>
+        <v>21.914812608</v>
       </c>
       <c r="Q95">
-        <v>22.30085417599999</v>
+        <v>22.085812608</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5510425365077496</v>
+        <v>0.6325642062176183</v>
       </c>
       <c r="T95">
-        <v>6.585003975989772</v>
+        <v>7.647504617521913</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.106555460232283</v>
+        <v>2.084145295761727</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08640521237305707</v>
+        <v>0.08630152719057169</v>
       </c>
       <c r="C96">
-        <v>80.65337783399383</v>
+        <v>77.64931889932382</v>
       </c>
       <c r="D96">
-        <v>456.2213778339939</v>
+        <v>457.3893188993239</v>
       </c>
       <c r="E96">
-        <v>217.7680000000001</v>
+        <v>221.9400000000001</v>
       </c>
       <c r="F96">
-        <v>392.1680000000001</v>
+        <v>396.3400000000001</v>
       </c>
       <c r="G96">
         <v>16.6</v>
@@ -9159,28 +9159,28 @@
         <v>61.954</v>
       </c>
       <c r="M96">
-        <v>29.72633440000001</v>
+        <v>30.04257200000001</v>
       </c>
       <c r="N96">
-        <v>32.22766559999999</v>
+        <v>31.91142799999999</v>
       </c>
       <c r="O96">
-        <v>10.312852992</v>
+        <v>10.21165696</v>
       </c>
       <c r="P96">
-        <v>21.914812608</v>
+        <v>21.69977103999999</v>
       </c>
       <c r="Q96">
-        <v>22.085812608</v>
+        <v>21.87077103999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6325642062176183</v>
+        <v>0.7466945438114345</v>
       </c>
       <c r="T96">
-        <v>7.647504617521913</v>
+        <v>9.135005515666911</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.084145295761727</v>
+        <v>2.062206924227392</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08630152719057169</v>
+        <v>0.08619784200808628</v>
       </c>
       <c r="C97">
-        <v>77.64931889932382</v>
+        <v>74.65125524442522</v>
       </c>
       <c r="D97">
-        <v>457.3893188993239</v>
+        <v>458.5632552444252</v>
       </c>
       <c r="E97">
-        <v>221.9400000000001</v>
+        <v>226.1120000000001</v>
       </c>
       <c r="F97">
-        <v>396.3400000000001</v>
+        <v>400.5120000000001</v>
       </c>
       <c r="G97">
         <v>16.6</v>
@@ -9241,28 +9241,28 @@
         <v>61.954</v>
       </c>
       <c r="M97">
-        <v>30.04257200000001</v>
+        <v>30.35880960000001</v>
       </c>
       <c r="N97">
-        <v>31.91142799999999</v>
+        <v>31.59519039999999</v>
       </c>
       <c r="O97">
-        <v>10.21165696</v>
+        <v>10.110460928</v>
       </c>
       <c r="P97">
-        <v>21.69977103999999</v>
+        <v>21.48472947199999</v>
       </c>
       <c r="Q97">
-        <v>21.87077103999999</v>
+        <v>21.65572947199999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7466945438114345</v>
+        <v>0.9178900502021589</v>
       </c>
       <c r="T97">
-        <v>9.135005515666911</v>
+        <v>11.36625686288441</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.062206924227392</v>
+        <v>2.040725602100024</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08619784200808629</v>
+        <v>0.08609415682560091</v>
       </c>
       <c r="C98">
-        <v>74.6512552444251</v>
+        <v>71.65923315057398</v>
       </c>
       <c r="D98">
-        <v>458.5632552444251</v>
+        <v>459.743233150574</v>
       </c>
       <c r="E98">
-        <v>226.112</v>
+        <v>230.284</v>
       </c>
       <c r="F98">
-        <v>400.512</v>
+        <v>404.684</v>
       </c>
       <c r="G98">
         <v>16.6</v>
@@ -9323,28 +9323,28 @@
         <v>61.954</v>
       </c>
       <c r="M98">
-        <v>30.3588096</v>
+        <v>30.67504720000001</v>
       </c>
       <c r="N98">
-        <v>31.5951904</v>
+        <v>31.2789528</v>
       </c>
       <c r="O98">
-        <v>10.110460928</v>
+        <v>10.009264896</v>
       </c>
       <c r="P98">
-        <v>21.484729472</v>
+        <v>21.26968790399999</v>
       </c>
       <c r="Q98">
-        <v>21.655729472</v>
+        <v>21.44068790399999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9178900502021565</v>
+        <v>1.203215894186696</v>
       </c>
       <c r="T98">
-        <v>11.36625686288438</v>
+        <v>15.08500910824686</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.040725602100024</v>
+        <v>2.019687193830952</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08609415682560091</v>
+        <v>0.09545335164311551</v>
       </c>
       <c r="C99">
-        <v>71.65923315057398</v>
+        <v>-19.1700889173685</v>
       </c>
       <c r="D99">
-        <v>459.743233150574</v>
+        <v>373.0859110826315</v>
       </c>
       <c r="E99">
-        <v>230.284</v>
+        <v>234.456</v>
       </c>
       <c r="F99">
-        <v>404.684</v>
+        <v>408.8560000000001</v>
       </c>
       <c r="G99">
         <v>16.6</v>
@@ -9405,45 +9405,45 @@
         <v>61.954</v>
       </c>
       <c r="M99">
-        <v>30.67504720000001</v>
+        <v>36.79704</v>
       </c>
       <c r="N99">
-        <v>31.2789528</v>
+        <v>25.15696</v>
       </c>
       <c r="O99">
-        <v>10.009264896</v>
+        <v>8.0502272</v>
       </c>
       <c r="P99">
-        <v>21.26968790399999</v>
+        <v>17.1067328</v>
       </c>
       <c r="Q99">
-        <v>21.44068790399999</v>
+        <v>17.2777328</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.203215894186696</v>
+        <v>1.773867582155775</v>
       </c>
       <c r="T99">
-        <v>15.08500910824686</v>
+        <v>22.52251359897182</v>
       </c>
       <c r="U99">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V99">
         <v>0.32</v>
       </c>
       <c r="W99">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y99">
-        <v>2.019687193830952</v>
+        <v>1.683668034167966</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09545335164311551</v>
+        <v>0.09544622646063013</v>
       </c>
       <c r="C100">
-        <v>-19.1700889173685</v>
+        <v>-23.28854395758589</v>
       </c>
       <c r="D100">
-        <v>373.0859110826315</v>
+        <v>373.1394560424141</v>
       </c>
       <c r="E100">
-        <v>234.456</v>
+        <v>238.628</v>
       </c>
       <c r="F100">
-        <v>408.8560000000001</v>
+        <v>413.028</v>
       </c>
       <c r="G100">
         <v>16.6</v>
@@ -9487,28 +9487,28 @@
         <v>61.954</v>
       </c>
       <c r="M100">
-        <v>36.79704</v>
+        <v>37.17252</v>
       </c>
       <c r="N100">
-        <v>25.15696</v>
+        <v>24.78148</v>
       </c>
       <c r="O100">
-        <v>8.0502272</v>
+        <v>7.930073600000001</v>
       </c>
       <c r="P100">
-        <v>17.1067328</v>
+        <v>16.8514064</v>
       </c>
       <c r="Q100">
-        <v>17.2777328</v>
+        <v>17.0224064</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.773867582155775</v>
+        <v>3.48582264606301</v>
       </c>
       <c r="T100">
-        <v>22.52251359897182</v>
+        <v>44.8350270711467</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.683668034167966</v>
+        <v>1.666661286348087</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09544622646063013</v>
-      </c>
-      <c r="C101">
-        <v>-23.28854395758589</v>
-      </c>
-      <c r="D101">
-        <v>373.1394560424141</v>
-      </c>
-      <c r="E101">
-        <v>238.628</v>
-      </c>
-      <c r="F101">
-        <v>413.028</v>
-      </c>
-      <c r="G101">
-        <v>16.6</v>
-      </c>
-      <c r="H101">
-        <v>242.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>62.125</v>
-      </c>
-      <c r="K101">
-        <v>0.171</v>
-      </c>
-      <c r="L101">
-        <v>61.954</v>
-      </c>
-      <c r="M101">
-        <v>37.17252</v>
-      </c>
-      <c r="N101">
-        <v>24.78148</v>
-      </c>
-      <c r="O101">
-        <v>7.930073600000001</v>
-      </c>
-      <c r="P101">
-        <v>16.8514064</v>
-      </c>
-      <c r="Q101">
-        <v>17.0224064</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.48582264606301</v>
-      </c>
-      <c r="T101">
-        <v>44.8350270711467</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.32</v>
-      </c>
-      <c r="W101">
-        <v>0.06119999999999999</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.666661286348087</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
